--- a/datagen/params/data_gen.xlsx
+++ b/datagen/params/data_gen.xlsx
@@ -1719,7 +1719,7 @@
       <c r="D5" s="7" t="inlineStr"/>
       <c r="E5" s="7" t="inlineStr">
         <is>
-          <t>null_ratio=10; allowed_values=["VIP", "STANDARD", "NEW"]</t>
+          <t>null_ratio=0.1; allowed_values=["VIP", "STANDARD", "NEW"]</t>
         </is>
       </c>
       <c r="F5" s="7" t="inlineStr"/>

--- a/datagen/params/data_gen.xlsx
+++ b/datagen/params/data_gen.xlsx
@@ -3,11 +3,11 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="25920" windowHeight="11475" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="25920" windowHeight="11475" tabRatio="600" firstSheet="0" activeTab="2" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Инструкция" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Constant List" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Constant List" sheetId="2" state="hidden" r:id="rId2"/>
     <sheet name="tables" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="analytics_db.company_groups" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="analytics_db.subjects" sheetId="5" state="visible" r:id="rId5"/>
@@ -115,7 +115,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="7">
+  <borders count="15">
     <border>
       <left/>
       <right/>
@@ -170,6 +170,115 @@
     </border>
     <border>
       <left/>
+      <right style="thin">
+        <color rgb="FFD9EAD3"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFD9EAD3"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFD9EAD3"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
       <right/>
       <top style="thin">
         <color rgb="FFD9EAD3"/>
@@ -188,24 +297,11 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FFD9EAD3"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFD9EAD3"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFD9EAD3"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -225,16 +321,7 @@
     <xf numFmtId="0" fontId="5" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -244,11 +331,622 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="26">
+    <dxf>
+      <font>
+        <name val="Calibri"/>
+        <b val="1"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <condense val="0"/>
+        <color auto="1"/>
+        <extend val="0"/>
+        <sz val="11"/>
+        <vertAlign val="baseline"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFDCE6F1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="top" wrapText="1"/>
+      <border outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="top" wrapText="1"/>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Calibri"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <condense val="0"/>
+        <color rgb="FF385723"/>
+        <extend val="0"/>
+        <sz val="11"/>
+        <vertAlign val="baseline"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFE2F0D9"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="top" wrapText="1"/>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Calibri"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <condense val="0"/>
+        <color rgb="FF385723"/>
+        <extend val="0"/>
+        <sz val="11"/>
+        <vertAlign val="baseline"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFE2F0D9"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="top" wrapText="1"/>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="top" wrapText="1"/>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="top" wrapText="1"/>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="top" wrapText="1"/>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="top" wrapText="1"/>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="top" wrapText="1"/>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="top" wrapText="1"/>
+      <border>
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Calibri"/>
+        <b val="1"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <condense val="0"/>
+        <color auto="1"/>
+        <extend val="0"/>
+        <sz val="11"/>
+        <vertAlign val="baseline"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFDCE6F1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="top" wrapText="1"/>
+      <border outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="top" wrapText="1"/>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Calibri"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <condense val="0"/>
+        <color rgb="FF385723"/>
+        <extend val="0"/>
+        <sz val="11"/>
+        <vertAlign val="baseline"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFE2F0D9"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="top" wrapText="1"/>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Calibri"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <condense val="0"/>
+        <color rgb="FF385723"/>
+        <extend val="0"/>
+        <sz val="11"/>
+        <vertAlign val="baseline"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFE2F0D9"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="top" wrapText="1"/>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="top" wrapText="1"/>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="top" wrapText="1"/>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="top" wrapText="1"/>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="top" wrapText="1"/>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="top" wrapText="1"/>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="top" wrapText="1"/>
+      <border>
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
@@ -319,6 +1017,48 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Таблица1" displayName="Таблица1" ref="A1:H5" headerRowCount="1" totalsRowShown="0" headerRowDxfId="13" dataDxfId="14" headerRowBorderDxfId="24" tableBorderDxfId="25" totalsRowBorderDxfId="23">
+  <autoFilter ref="A1:H5"/>
+  <tableColumns count="8">
+    <tableColumn id="1" name="column_name" dataDxfId="22"/>
+    <tableColumn id="2" name="gen_data_type" dataDxfId="21"/>
+    <tableColumn id="3" name="output_data_type" dataDxfId="20"/>
+    <tableColumn id="4" name="is_primary_key" dataDxfId="19"/>
+    <tableColumn id="5" name="constraints" dataDxfId="18"/>
+    <tableColumn id="6" name="foreign_key" dataDxfId="17"/>
+    <tableColumn id="7" name="Подсказка по constraints" dataDxfId="16">
+      <calculatedColumnFormula>IF($F2&lt;&gt;"","Для foreign_key допустим только null_ratio=0..1. Остальные generator constraints запрещены.",IFERROR(VLOOKUP($B2,'Constant List'!$A$2:$B$7,2,FALSE),"Тип данных не заполнен"))</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="8" name="Пример заполнения foreign_key" dataDxfId="15">
+      <calculatedColumnFormula>'Constant List'!$J$2</calculatedColumnFormula>
+    </tableColumn>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Таблица2" displayName="Таблица2" ref="A1:H8" headerRowCount="1" totalsRowShown="0" headerRowDxfId="0" dataDxfId="1" headerRowBorderDxfId="11" tableBorderDxfId="12" totalsRowBorderDxfId="10">
+  <autoFilter ref="A1:H8"/>
+  <tableColumns count="8">
+    <tableColumn id="1" name="column_name" dataDxfId="9"/>
+    <tableColumn id="2" name="gen_data_type" dataDxfId="8"/>
+    <tableColumn id="3" name="output_data_type" dataDxfId="7"/>
+    <tableColumn id="4" name="is_primary_key" dataDxfId="6"/>
+    <tableColumn id="5" name="constraints" dataDxfId="5"/>
+    <tableColumn id="6" name="foreign_key" dataDxfId="4"/>
+    <tableColumn id="7" name="Подсказка по constraints" dataDxfId="3">
+      <calculatedColumnFormula>IF($F2&lt;&gt;"","Для foreign_key допустим только null_ratio=0..1. Остальные generator constraints запрещены.",IFERROR(VLOOKUP($B2,'Constant List'!$A$2:$B$7,2,FALSE),"Тип данных не заполнен"))</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="8" name="Пример заполнения foreign_key" dataDxfId="2">
+      <calculatedColumnFormula>'Constant List'!$J$2</calculatedColumnFormula>
+    </tableColumn>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -613,20 +1353,20 @@
   <dimension ref="A1:B61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.25"/>
   <cols>
-    <col width="34" customWidth="1" style="8" min="1" max="1"/>
-    <col width="120" customWidth="1" style="8" min="2" max="2"/>
+    <col width="34" customWidth="1" style="7" min="1" max="1"/>
+    <col width="120" customWidth="1" style="7" min="2" max="2"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1" s="8">
-      <c r="A1" s="7" t="inlineStr">
+    <row r="1" ht="26" customHeight="1" s="7">
+      <c r="A1" s="11" t="inlineStr">
         <is>
           <t>Шаблон DataGen: как заполнять Excel</t>
         </is>
       </c>
-      <c r="B1" s="14" t="n"/>
-    </row>
-    <row r="2" ht="10.05" customHeight="1" s="8"/>
-    <row r="3" ht="22.05" customHeight="1" s="8">
+      <c r="B1" s="12" t="n"/>
+    </row>
+    <row r="2" ht="10.05" customHeight="1" s="7"/>
+    <row r="3" ht="22.05" customHeight="1" s="7">
       <c r="A3" s="4" t="inlineStr">
         <is>
           <t>Шаг 1</t>
@@ -638,7 +1378,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="22.05" customHeight="1" s="8">
+    <row r="4" ht="22.05" customHeight="1" s="7">
       <c r="A4" s="4" t="inlineStr">
         <is>
           <t>Шаг 2</t>
@@ -650,7 +1390,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="30" customHeight="1" s="8">
+    <row r="5" ht="30" customHeight="1" s="7">
       <c r="A5" s="4" t="inlineStr">
         <is>
           <t>Шаг 3</t>
@@ -662,7 +1402,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="22.05" customHeight="1" s="8">
+    <row r="6" ht="22.05" customHeight="1" s="7">
       <c r="A6" s="4" t="inlineStr">
         <is>
           <t>Шаг 4</t>
@@ -674,7 +1414,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="22.05" customHeight="1" s="8">
+    <row r="7" ht="22.05" customHeight="1" s="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
           <t>Шаг 5</t>
@@ -686,7 +1426,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="22.05" customHeight="1" s="8">
+    <row r="8" ht="22.05" customHeight="1" s="7">
       <c r="A8" s="4" t="inlineStr">
         <is>
           <t>Шаг 6</t>
@@ -698,7 +1438,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="30" customHeight="1" s="8">
+    <row r="9" ht="30" customHeight="1" s="7">
       <c r="A9" s="4" t="inlineStr">
         <is>
           <t>Шаг 7</t>
@@ -710,7 +1450,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="22.05" customHeight="1" s="8">
+    <row r="10" ht="22.05" customHeight="1" s="7">
       <c r="A10" s="4" t="inlineStr">
         <is>
           <t>Шаг 8</t>
@@ -722,7 +1462,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="30" customHeight="1" s="8">
+    <row r="11" ht="30" customHeight="1" s="7">
       <c r="A11" s="4" t="inlineStr">
         <is>
           <t>Шаг 9</t>
@@ -734,8 +1474,8 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="10.05" customHeight="1" s="8"/>
-    <row r="13" ht="24" customHeight="1" s="8">
+    <row r="12" ht="10.05" customHeight="1" s="7"/>
+    <row r="13" ht="24" customHeight="1" s="7">
       <c r="A13" s="6" t="inlineStr">
         <is>
           <t>Общие колонки</t>
@@ -743,7 +1483,7 @@
       </c>
       <c r="B13" s="6" t="n"/>
     </row>
-    <row r="14" ht="22.05" customHeight="1" s="8">
+    <row r="14" ht="22.05" customHeight="1" s="7">
       <c r="A14" s="4" t="inlineStr">
         <is>
           <t>column_name</t>
@@ -755,7 +1495,7 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="22.05" customHeight="1" s="8">
+    <row r="15" ht="22.05" customHeight="1" s="7">
       <c r="A15" s="4" t="inlineStr">
         <is>
           <t>gen_data_type</t>
@@ -767,7 +1507,7 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="22.05" customHeight="1" s="8">
+    <row r="16" ht="22.05" customHeight="1" s="7">
       <c r="A16" s="4" t="inlineStr">
         <is>
           <t>output_data_type</t>
@@ -779,7 +1519,7 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="30" customHeight="1" s="8">
+    <row r="17" ht="30" customHeight="1" s="7">
       <c r="A17" s="4" t="inlineStr">
         <is>
           <t>is_primary_key</t>
@@ -791,7 +1531,7 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="22.05" customHeight="1" s="8">
+    <row r="18" ht="22.05" customHeight="1" s="7">
       <c r="A18" s="4" t="inlineStr">
         <is>
           <t>constraints</t>
@@ -803,7 +1543,7 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="22.05" customHeight="1" s="8">
+    <row r="19" ht="22.05" customHeight="1" s="7">
       <c r="A19" s="4" t="inlineStr">
         <is>
           <t>foreign_key</t>
@@ -815,8 +1555,8 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="10.05" customHeight="1" s="8"/>
-    <row r="21" ht="24" customHeight="1" s="8">
+    <row r="20" ht="10.05" customHeight="1" s="7"/>
+    <row r="21" ht="24" customHeight="1" s="7">
       <c r="A21" s="6" t="inlineStr">
         <is>
           <t>Общие constraints</t>
@@ -824,7 +1564,7 @@
       </c>
       <c r="B21" s="6" t="n"/>
     </row>
-    <row r="22" ht="22.05" customHeight="1" s="8">
+    <row r="22" ht="22.05" customHeight="1" s="7">
       <c r="A22" s="4" t="inlineStr">
         <is>
           <t>null_ratio</t>
@@ -836,7 +1576,7 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="22.05" customHeight="1" s="8">
+    <row r="23" ht="22.05" customHeight="1" s="7">
       <c r="A23" s="4" t="inlineStr">
         <is>
           <t>is_unique</t>
@@ -848,7 +1588,7 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="30" customHeight="1" s="8">
+    <row r="24" ht="30" customHeight="1" s="7">
       <c r="A24" s="4" t="inlineStr">
         <is>
           <t>allowed_values</t>
@@ -860,8 +1600,8 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="10.05" customHeight="1" s="8"/>
-    <row r="26" ht="24" customHeight="1" s="8">
+    <row r="25" ht="10.05" customHeight="1" s="7"/>
+    <row r="26" ht="24" customHeight="1" s="7">
       <c r="A26" s="6" t="inlineStr">
         <is>
           <t>STRING constraints</t>
@@ -869,7 +1609,7 @@
       </c>
       <c r="B26" s="6" t="n"/>
     </row>
-    <row r="27" ht="22.05" customHeight="1" s="8">
+    <row r="27" ht="22.05" customHeight="1" s="7">
       <c r="A27" s="4" t="inlineStr">
         <is>
           <t>length</t>
@@ -881,7 +1621,7 @@
         </is>
       </c>
     </row>
-    <row r="28" ht="30" customHeight="1" s="8">
+    <row r="28" ht="30" customHeight="1" s="7">
       <c r="A28" s="4" t="inlineStr">
         <is>
           <t>character_set</t>
@@ -893,7 +1633,7 @@
         </is>
       </c>
     </row>
-    <row r="29" ht="30" customHeight="1" s="8">
+    <row r="29" ht="30" customHeight="1" s="7">
       <c r="A29" s="4" t="inlineStr">
         <is>
           <t>case_mode</t>
@@ -905,7 +1645,7 @@
         </is>
       </c>
     </row>
-    <row r="30" ht="22.05" customHeight="1" s="8">
+    <row r="30" ht="22.05" customHeight="1" s="7">
       <c r="A30" s="4" t="inlineStr">
         <is>
           <t>regular_expr</t>
@@ -917,8 +1657,8 @@
         </is>
       </c>
     </row>
-    <row r="31" ht="10.05" customHeight="1" s="8"/>
-    <row r="32" ht="24" customHeight="1" s="8">
+    <row r="31" ht="10.05" customHeight="1" s="7"/>
+    <row r="32" ht="24" customHeight="1" s="7">
       <c r="A32" s="6" t="inlineStr">
         <is>
           <t>INT / FLOAT constraints</t>
@@ -926,7 +1666,7 @@
       </c>
       <c r="B32" s="6" t="n"/>
     </row>
-    <row r="33" ht="22.05" customHeight="1" s="8">
+    <row r="33" ht="22.05" customHeight="1" s="7">
       <c r="A33" s="4" t="inlineStr">
         <is>
           <t>min_value</t>
@@ -938,7 +1678,7 @@
         </is>
       </c>
     </row>
-    <row r="34" ht="22.05" customHeight="1" s="8">
+    <row r="34" ht="22.05" customHeight="1" s="7">
       <c r="A34" s="4" t="inlineStr">
         <is>
           <t>max_value</t>
@@ -950,7 +1690,7 @@
         </is>
       </c>
     </row>
-    <row r="35" ht="22.05" customHeight="1" s="8">
+    <row r="35" ht="22.05" customHeight="1" s="7">
       <c r="A35" s="4" t="inlineStr">
         <is>
           <t>precision</t>
@@ -962,8 +1702,8 @@
         </is>
       </c>
     </row>
-    <row r="36" ht="10.05" customHeight="1" s="8"/>
-    <row r="37" ht="24" customHeight="1" s="8">
+    <row r="36" ht="10.05" customHeight="1" s="7"/>
+    <row r="37" ht="24" customHeight="1" s="7">
       <c r="A37" s="6" t="inlineStr">
         <is>
           <t>DATE constraints</t>
@@ -971,7 +1711,7 @@
       </c>
       <c r="B37" s="6" t="n"/>
     </row>
-    <row r="38" ht="22.05" customHeight="1" s="8">
+    <row r="38" ht="22.05" customHeight="1" s="7">
       <c r="A38" s="4" t="inlineStr">
         <is>
           <t>min_value</t>
@@ -983,7 +1723,7 @@
         </is>
       </c>
     </row>
-    <row r="39" ht="22.05" customHeight="1" s="8">
+    <row r="39" ht="22.05" customHeight="1" s="7">
       <c r="A39" s="4" t="inlineStr">
         <is>
           <t>max_value</t>
@@ -995,7 +1735,7 @@
         </is>
       </c>
     </row>
-    <row r="40" ht="30" customHeight="1" s="8">
+    <row r="40" ht="30" customHeight="1" s="7">
       <c r="A40" s="4" t="inlineStr">
         <is>
           <t>date_format</t>
@@ -1007,8 +1747,8 @@
         </is>
       </c>
     </row>
-    <row r="41" ht="10.05" customHeight="1" s="8"/>
-    <row r="42" ht="24" customHeight="1" s="8">
+    <row r="41" ht="10.05" customHeight="1" s="7"/>
+    <row r="42" ht="24" customHeight="1" s="7">
       <c r="A42" s="6" t="inlineStr">
         <is>
           <t>TIMESTAMP constraints</t>
@@ -1016,7 +1756,7 @@
       </c>
       <c r="B42" s="6" t="n"/>
     </row>
-    <row r="43" ht="22.05" customHeight="1" s="8">
+    <row r="43" ht="22.05" customHeight="1" s="7">
       <c r="A43" s="4" t="inlineStr">
         <is>
           <t>min_timestamp</t>
@@ -1028,7 +1768,7 @@
         </is>
       </c>
     </row>
-    <row r="44" ht="22.05" customHeight="1" s="8">
+    <row r="44" ht="22.05" customHeight="1" s="7">
       <c r="A44" s="4" t="inlineStr">
         <is>
           <t>max_timestamp</t>
@@ -1040,7 +1780,7 @@
         </is>
       </c>
     </row>
-    <row r="45" ht="22.05" customHeight="1" s="8">
+    <row r="45" ht="22.05" customHeight="1" s="7">
       <c r="A45" s="4" t="inlineStr">
         <is>
           <t>timestamp_format</t>
@@ -1052,8 +1792,8 @@
         </is>
       </c>
     </row>
-    <row r="46" ht="10.05" customHeight="1" s="8"/>
-    <row r="47" ht="24" customHeight="1" s="8">
+    <row r="46" ht="10.05" customHeight="1" s="7"/>
+    <row r="47" ht="24" customHeight="1" s="7">
       <c r="A47" s="6" t="inlineStr">
         <is>
           <t>BOOLEAN constraints</t>
@@ -1061,7 +1801,7 @@
       </c>
       <c r="B47" s="6" t="n"/>
     </row>
-    <row r="48" ht="22.05" customHeight="1" s="8">
+    <row r="48" ht="22.05" customHeight="1" s="7">
       <c r="A48" s="4" t="inlineStr">
         <is>
           <t>allowed_values</t>
@@ -1073,8 +1813,8 @@
         </is>
       </c>
     </row>
-    <row r="49" ht="10.05" customHeight="1" s="8"/>
-    <row r="50" ht="24" customHeight="1" s="8">
+    <row r="49" ht="10.05" customHeight="1" s="7"/>
+    <row r="50" ht="24" customHeight="1" s="7">
       <c r="A50" s="6" t="inlineStr">
         <is>
           <t>Foreign Key</t>
@@ -1082,7 +1822,7 @@
       </c>
       <c r="B50" s="6" t="n"/>
     </row>
-    <row r="51" ht="30" customHeight="1" s="8">
+    <row r="51" ht="30" customHeight="1" s="7">
       <c r="A51" s="4" t="inlineStr">
         <is>
           <t>foreign_key</t>
@@ -1094,7 +1834,7 @@
         </is>
       </c>
     </row>
-    <row r="52" ht="36" customHeight="1" s="8">
+    <row r="52" ht="36" customHeight="1" s="7">
       <c r="A52" s="4" t="inlineStr">
         <is>
           <t>relation_type</t>
@@ -1106,7 +1846,7 @@
         </is>
       </c>
     </row>
-    <row r="53" ht="22.05" customHeight="1" s="8">
+    <row r="53" ht="22.05" customHeight="1" s="7">
       <c r="A53" s="4" t="inlineStr">
         <is>
           <t>Ограничение</t>
@@ -1118,8 +1858,8 @@
         </is>
       </c>
     </row>
-    <row r="54" ht="10.05" customHeight="1" s="8"/>
-    <row r="55" ht="24" customHeight="1" s="8">
+    <row r="54" ht="10.05" customHeight="1" s="7"/>
+    <row r="55" ht="24" customHeight="1" s="7">
       <c r="A55" s="6" t="inlineStr">
         <is>
           <t>Разрешенные output_data_type</t>
@@ -1127,7 +1867,7 @@
       </c>
       <c r="B55" s="6" t="n"/>
     </row>
-    <row r="56" ht="22.05" customHeight="1" s="8">
+    <row r="56" ht="22.05" customHeight="1" s="7">
       <c r="A56" s="4" t="inlineStr">
         <is>
           <t>STRING</t>
@@ -1139,7 +1879,7 @@
         </is>
       </c>
     </row>
-    <row r="57" ht="22.05" customHeight="1" s="8">
+    <row r="57" ht="22.05" customHeight="1" s="7">
       <c r="A57" s="4" t="inlineStr">
         <is>
           <t>INT</t>
@@ -1151,7 +1891,7 @@
         </is>
       </c>
     </row>
-    <row r="58" ht="22.05" customHeight="1" s="8">
+    <row r="58" ht="22.05" customHeight="1" s="7">
       <c r="A58" s="4" t="inlineStr">
         <is>
           <t>FLOAT</t>
@@ -1163,7 +1903,7 @@
         </is>
       </c>
     </row>
-    <row r="59" ht="22.05" customHeight="1" s="8">
+    <row r="59" ht="22.05" customHeight="1" s="7">
       <c r="A59" s="4" t="inlineStr">
         <is>
           <t>DATE</t>
@@ -1175,7 +1915,7 @@
         </is>
       </c>
     </row>
-    <row r="60" ht="22.05" customHeight="1" s="8">
+    <row r="60" ht="22.05" customHeight="1" s="7">
       <c r="A60" s="4" t="inlineStr">
         <is>
           <t>TIMESTAMP</t>
@@ -1187,7 +1927,7 @@
         </is>
       </c>
     </row>
-    <row r="61" ht="22.05" customHeight="1" s="8">
+    <row r="61" ht="22.05" customHeight="1" s="7">
       <c r="A61" s="4" t="inlineStr">
         <is>
           <t>BOOLEAN</t>
@@ -1216,8 +1956,8 @@
   <dimension ref="A1:R7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.25"/>
   <cols>
-    <col width="63.265625" customWidth="1" style="8" min="2" max="2"/>
-    <col width="24.06640625" customWidth="1" style="8" min="10" max="10"/>
+    <col width="63.265625" customWidth="1" style="7" min="2" max="2"/>
+    <col width="24.06640625" customWidth="1" style="7" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1272,13 +2012,13 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="114" customHeight="1" s="8">
+    <row r="2" ht="114" customHeight="1" s="7">
       <c r="A2" t="inlineStr">
         <is>
           <t>STRING</t>
         </is>
       </c>
-      <c r="B2" s="13" t="inlineStr">
+      <c r="B2" s="10" t="inlineStr">
         <is>
           <t>Формат constraints: 
 null_ratio=0..1; 
@@ -1295,7 +2035,7 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="J2" s="13" t="inlineStr">
+      <c r="J2" s="10" t="inlineStr">
         <is>
           <t>schema_name="analytics_db"; 
 table_name="company_groups"; 
@@ -1334,13 +2074,13 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="85.5" customHeight="1" s="8">
+    <row r="3" ht="85.5" customHeight="1" s="7">
       <c r="A3" t="inlineStr">
         <is>
           <t>INT</t>
         </is>
       </c>
-      <c r="B3" s="13" t="inlineStr">
+      <c r="B3" s="10" t="inlineStr">
         <is>
           <t>Формат constraints: 
 null_ratio=0..1; 
@@ -1386,13 +2126,13 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="99.75" customHeight="1" s="8">
+    <row r="4" ht="99.75" customHeight="1" s="7">
       <c r="A4" t="inlineStr">
         <is>
           <t>FLOAT</t>
         </is>
       </c>
-      <c r="B4" s="13" t="inlineStr">
+      <c r="B4" s="10" t="inlineStr">
         <is>
           <t>Формат constraints:
 null_ratio=0..1; 
@@ -1429,13 +2169,13 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="99.75" customHeight="1" s="8">
+    <row r="5" ht="99.75" customHeight="1" s="7">
       <c r="A5" t="inlineStr">
         <is>
           <t>DATE</t>
         </is>
       </c>
-      <c r="B5" s="13" t="inlineStr">
+      <c r="B5" s="10" t="inlineStr">
         <is>
           <t>Формат constraints: 
 null_ratio=0..1; 
@@ -1462,13 +2202,13 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="99.75" customHeight="1" s="8">
+    <row r="6" ht="99.75" customHeight="1" s="7">
       <c r="A6" t="inlineStr">
         <is>
           <t>TIMESTAMP</t>
         </is>
       </c>
-      <c r="B6" s="13" t="inlineStr">
+      <c r="B6" s="10" t="inlineStr">
         <is>
           <t>Формат constraints: 
 null_ratio=0..1; 
@@ -1480,13 +2220,13 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="57" customHeight="1" s="8">
+    <row r="7" ht="57" customHeight="1" s="7">
       <c r="A7" t="inlineStr">
         <is>
           <t>BOOLEAN</t>
         </is>
       </c>
-      <c r="B7" s="13" t="inlineStr">
+      <c r="B7" s="10" t="inlineStr">
         <is>
           <t>Формат constraints: 
 null_ratio=0..1; 
@@ -1509,8 +2249,8 @@
   <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.25"/>
   <cols>
-    <col width="18" customWidth="1" style="8" min="1" max="2"/>
-    <col width="12" customWidth="1" style="8" min="3" max="3"/>
+    <col width="18" customWidth="1" style="7" min="1" max="2"/>
+    <col width="12" customWidth="1" style="7" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1537,7 +2277,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="24" customHeight="1" s="8">
+    <row r="6" ht="24" customHeight="1" s="7">
       <c r="A6" s="3" t="inlineStr">
         <is>
           <t>schema_name</t>
@@ -1598,176 +2338,184 @@
   <dimension ref="A1:H5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.25"/>
   <cols>
-    <col width="12.33203125" bestFit="1" customWidth="1" style="8" min="1" max="1"/>
-    <col width="12.9296875" bestFit="1" customWidth="1" style="8" min="2" max="2"/>
-    <col width="15.53125" bestFit="1" customWidth="1" style="8" min="3" max="3"/>
-    <col width="13.1328125" bestFit="1" customWidth="1" style="8" min="4" max="4"/>
-    <col width="20.46484375" customWidth="1" style="8" min="5" max="5"/>
-    <col width="20.59765625" customWidth="1" style="8" min="6" max="6"/>
-    <col width="38.06640625" customWidth="1" style="8" min="7" max="7"/>
-    <col width="39.6640625" customWidth="1" style="8" min="8" max="8"/>
+    <col width="14.59765625" customWidth="1" style="7" min="1" max="1"/>
+    <col width="14.73046875" customWidth="1" style="7" min="2" max="2"/>
+    <col width="17.33203125" customWidth="1" style="7" min="3" max="3"/>
+    <col width="14.9296875" customWidth="1" style="7" min="4" max="4"/>
+    <col width="20.46484375" customWidth="1" style="7" min="5" max="5"/>
+    <col width="20.59765625" customWidth="1" style="7" min="6" max="6"/>
+    <col width="38.06640625" customWidth="1" style="7" min="7" max="7"/>
+    <col width="39.6640625" customWidth="1" style="7" min="8" max="8"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1" s="8">
-      <c r="A1" s="9" t="inlineStr">
+    <row r="1" ht="30" customHeight="1" s="7">
+      <c r="A1" s="15" t="inlineStr">
         <is>
           <t>column_name</t>
         </is>
       </c>
-      <c r="B1" s="9" t="inlineStr">
+      <c r="B1" s="16" t="inlineStr">
         <is>
           <t>gen_data_type</t>
         </is>
       </c>
-      <c r="C1" s="9" t="inlineStr">
+      <c r="C1" s="16" t="inlineStr">
         <is>
           <t>output_data_type</t>
         </is>
       </c>
-      <c r="D1" s="9" t="inlineStr">
+      <c r="D1" s="16" t="inlineStr">
         <is>
           <t>is_primary_key</t>
         </is>
       </c>
-      <c r="E1" s="9" t="inlineStr">
+      <c r="E1" s="16" t="inlineStr">
         <is>
           <t>constraints</t>
         </is>
       </c>
-      <c r="F1" s="9" t="inlineStr">
+      <c r="F1" s="16" t="inlineStr">
         <is>
           <t>foreign_key</t>
         </is>
       </c>
-      <c r="G1" s="10" t="inlineStr">
+      <c r="G1" s="17" t="inlineStr">
         <is>
           <t>Подсказка по constraints</t>
         </is>
       </c>
-      <c r="H1" s="10" t="inlineStr">
+      <c r="H1" s="18" t="inlineStr">
         <is>
           <t>Пример заполнения foreign_key</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="114" customHeight="1" s="8">
-      <c r="A2" s="11" t="inlineStr">
+    <row r="2" ht="114" customHeight="1" s="7">
+      <c r="A2" s="13" t="inlineStr">
         <is>
           <t>INN</t>
         </is>
       </c>
-      <c r="B2" s="11" t="inlineStr">
-        <is>
-          <t>STRING</t>
-        </is>
-      </c>
-      <c r="C2" s="11" t="inlineStr">
+      <c r="B2" s="8" t="inlineStr">
         <is>
           <t>INT</t>
         </is>
       </c>
-      <c r="D2" s="11" t="b">
+      <c r="C2" s="8" t="inlineStr">
+        <is>
+          <t>INT</t>
+        </is>
+      </c>
+      <c r="D2" s="8" t="b">
         <v>1</v>
       </c>
-      <c r="E2" s="11" t="inlineStr">
-        <is>
-          <t>null_ratio=0; is_unique=true; length=10; character_set="digits"</t>
-        </is>
-      </c>
-      <c r="F2" s="11" t="n"/>
-      <c r="G2" s="12">
+      <c r="E2" s="8" t="inlineStr">
+        <is>
+          <t>digits_count=10</t>
+        </is>
+      </c>
+      <c r="F2" s="8" t="n"/>
+      <c r="G2" s="9">
         <f>IF($F2&lt;&gt;"","Для foreign_key допустим только null_ratio=0..1. Остальные generator constraints запрещены.",IFERROR(VLOOKUP($B2,'Constant List'!$A$2:$B$7,2,FALSE),"Тип данных не заполнен"))</f>
         <v/>
       </c>
-      <c r="H2" s="12">
+      <c r="H2" s="14">
         <f>'Constant List'!$J$2</f>
         <v/>
       </c>
     </row>
-    <row r="3" ht="85.5" customHeight="1" s="8">
-      <c r="A3" s="11" t="inlineStr">
+    <row r="3" ht="85.5" customHeight="1" s="7">
+      <c r="A3" s="13" t="inlineStr">
         <is>
           <t>GROUP_ID_DM</t>
         </is>
       </c>
-      <c r="B3" s="11" t="inlineStr">
+      <c r="B3" s="8" t="inlineStr">
         <is>
           <t>INT</t>
         </is>
       </c>
-      <c r="C3" s="11" t="n"/>
-      <c r="D3" s="11" t="n"/>
-      <c r="E3" s="11" t="inlineStr">
+      <c r="C3" s="8" t="inlineStr">
+        <is>
+          <t>INT</t>
+        </is>
+      </c>
+      <c r="D3" s="8" t="n"/>
+      <c r="E3" s="8" t="inlineStr">
         <is>
           <t>null_ratio=0; min_value=1; max_value=6000000</t>
         </is>
       </c>
-      <c r="F3" s="11" t="n"/>
-      <c r="G3" s="12">
+      <c r="F3" s="8" t="n"/>
+      <c r="G3" s="9">
         <f>IF($F3&lt;&gt;"","Для foreign_key допустим только null_ratio=0..1. Остальные generator constraints запрещены.",IFERROR(VLOOKUP($B3,'Constant List'!$A$2:$B$7,2,FALSE),"Тип данных не заполнен"))</f>
         <v/>
       </c>
-      <c r="H3" s="12">
+      <c r="H3" s="14">
         <f>'Constant List'!$J$2</f>
         <v/>
       </c>
     </row>
-    <row r="4" ht="85.5" customHeight="1" s="8">
-      <c r="A4" s="11" t="inlineStr">
+    <row r="4" ht="85.5" customHeight="1" s="7">
+      <c r="A4" s="13" t="inlineStr">
         <is>
           <t>MAIN_COMPANY_FLG_DM</t>
         </is>
       </c>
-      <c r="B4" s="11" t="inlineStr">
+      <c r="B4" s="8" t="inlineStr">
         <is>
           <t>INT</t>
         </is>
       </c>
-      <c r="C4" s="11" t="n"/>
-      <c r="D4" s="11" t="n"/>
-      <c r="E4" s="11" t="inlineStr">
+      <c r="C4" s="8" t="inlineStr">
+        <is>
+          <t>INT</t>
+        </is>
+      </c>
+      <c r="D4" s="8" t="n"/>
+      <c r="E4" s="8" t="inlineStr">
         <is>
           <t>allowed_values=[0, 1]</t>
         </is>
       </c>
-      <c r="F4" s="11" t="n"/>
-      <c r="G4" s="12">
+      <c r="F4" s="8" t="n"/>
+      <c r="G4" s="9">
         <f>IF($F4&lt;&gt;"","Для foreign_key допустим только null_ratio=0..1. Остальные generator constraints запрещены.",IFERROR(VLOOKUP($B4,'Constant List'!$A$2:$B$7,2,FALSE),"Тип данных не заполнен"))</f>
         <v/>
       </c>
-      <c r="H4" s="12">
+      <c r="H4" s="14">
         <f>'Constant List'!$J$2</f>
         <v/>
       </c>
     </row>
-    <row r="5" ht="99.75" customHeight="1" s="8">
-      <c r="A5" s="11" t="inlineStr">
+    <row r="5" ht="99.75" customHeight="1" s="7">
+      <c r="A5" s="19" t="inlineStr">
         <is>
           <t>VALUE_DAY</t>
         </is>
       </c>
-      <c r="B5" s="11" t="inlineStr">
+      <c r="B5" s="20" t="inlineStr">
         <is>
           <t>DATE</t>
         </is>
       </c>
-      <c r="C5" s="11" t="inlineStr">
+      <c r="C5" s="20" t="inlineStr">
         <is>
           <t>INT</t>
         </is>
       </c>
-      <c r="D5" s="11" t="n"/>
-      <c r="E5" s="11" t="inlineStr">
+      <c r="D5" s="20" t="n"/>
+      <c r="E5" s="20" t="inlineStr">
         <is>
           <t>date_format="%Y%m%d"</t>
         </is>
       </c>
-      <c r="F5" s="11" t="n"/>
-      <c r="G5" s="12">
+      <c r="F5" s="20" t="n"/>
+      <c r="G5" s="21">
         <f>IF($F5&lt;&gt;"","Для foreign_key допустим только null_ratio=0..1. Остальные generator constraints запрещены.",IFERROR(VLOOKUP($B5,'Constant List'!$A$2:$B$7,2,FALSE),"Тип данных не заполнен"))</f>
         <v/>
       </c>
-      <c r="H5" s="12">
+      <c r="H5" s="22">
         <f>'Constant List'!$J$2</f>
         <v/>
       </c>
@@ -1785,6 +2533,9 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>
 
@@ -1797,250 +2548,278 @@
   <dimension ref="A1:H8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.25"/>
   <cols>
-    <col width="12.33203125" bestFit="1" customWidth="1" style="8" min="1" max="1"/>
-    <col width="12.9296875" bestFit="1" customWidth="1" style="8" min="2" max="2"/>
-    <col width="15.53125" bestFit="1" customWidth="1" style="8" min="3" max="3"/>
-    <col width="13.1328125" bestFit="1" customWidth="1" style="8" min="4" max="4"/>
-    <col width="21" customWidth="1" style="8" min="5" max="5"/>
-    <col width="26.33203125" customWidth="1" style="8" min="6" max="6"/>
-    <col width="57.59765625" customWidth="1" style="8" min="7" max="7"/>
-    <col width="38.6640625" bestFit="1" customWidth="1" style="8" min="8" max="8"/>
+    <col width="14.19921875" customWidth="1" style="7" min="1" max="1"/>
+    <col width="14.73046875" customWidth="1" style="7" min="2" max="2"/>
+    <col width="17.33203125" customWidth="1" style="7" min="3" max="3"/>
+    <col width="14.9296875" customWidth="1" style="7" min="4" max="4"/>
+    <col width="21" customWidth="1" style="7" min="5" max="5"/>
+    <col width="26.33203125" customWidth="1" style="7" min="6" max="6"/>
+    <col width="57.59765625" customWidth="1" style="7" min="7" max="7"/>
+    <col width="38.6640625" bestFit="1" customWidth="1" style="7" min="8" max="8"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1" s="8">
-      <c r="A1" s="9" t="inlineStr">
+    <row r="1" ht="30" customHeight="1" s="7">
+      <c r="A1" s="15" t="inlineStr">
         <is>
           <t>column_name</t>
         </is>
       </c>
-      <c r="B1" s="9" t="inlineStr">
+      <c r="B1" s="16" t="inlineStr">
         <is>
           <t>gen_data_type</t>
         </is>
       </c>
-      <c r="C1" s="9" t="inlineStr">
+      <c r="C1" s="16" t="inlineStr">
         <is>
           <t>output_data_type</t>
         </is>
       </c>
-      <c r="D1" s="9" t="inlineStr">
+      <c r="D1" s="16" t="inlineStr">
         <is>
           <t>is_primary_key</t>
         </is>
       </c>
-      <c r="E1" s="9" t="inlineStr">
+      <c r="E1" s="16" t="inlineStr">
         <is>
           <t>constraints</t>
         </is>
       </c>
-      <c r="F1" s="9" t="inlineStr">
+      <c r="F1" s="16" t="inlineStr">
         <is>
           <t>foreign_key</t>
         </is>
       </c>
-      <c r="G1" s="10" t="inlineStr">
+      <c r="G1" s="17" t="inlineStr">
         <is>
           <t>Подсказка по constraints</t>
         </is>
       </c>
-      <c r="H1" s="10" t="inlineStr">
+      <c r="H1" s="18" t="inlineStr">
         <is>
           <t>Пример заполнения foreign_key</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="128.25" customHeight="1" s="8">
-      <c r="A2" s="11" t="inlineStr">
+    <row r="2" ht="128.25" customHeight="1" s="7">
+      <c r="A2" s="13" t="inlineStr">
         <is>
           <t>STYPE</t>
         </is>
       </c>
-      <c r="B2" s="11" t="inlineStr">
+      <c r="B2" s="8" t="inlineStr">
         <is>
           <t>STRING</t>
         </is>
       </c>
-      <c r="C2" s="11" t="n"/>
-      <c r="D2" s="11" t="n"/>
-      <c r="E2" s="11" t="inlineStr">
+      <c r="C2" s="8" t="inlineStr">
+        <is>
+          <t>STRING</t>
+        </is>
+      </c>
+      <c r="D2" s="8" t="n"/>
+      <c r="E2" s="8" t="inlineStr">
         <is>
           <t>allowed_values=["c", "cpr"]</t>
         </is>
       </c>
-      <c r="F2" s="11" t="n"/>
-      <c r="G2" s="12">
+      <c r="F2" s="8" t="n"/>
+      <c r="G2" s="9">
         <f>IF($F2&lt;&gt;"","Для foreign_key допустим только null_ratio=0..1. Остальные generator constraints запрещены.",IFERROR(VLOOKUP($B2,'Constant List'!$A$2:$B$7,2,FALSE),"Тип данных не заполнен"))</f>
         <v/>
       </c>
-      <c r="H2" s="12">
+      <c r="H2" s="14">
         <f>'Constant List'!$J$2</f>
         <v/>
       </c>
     </row>
-    <row r="3" ht="57" customHeight="1" s="8">
-      <c r="A3" s="11" t="inlineStr">
+    <row r="3" ht="57" customHeight="1" s="7">
+      <c r="A3" s="13" t="inlineStr">
         <is>
           <t>SINN</t>
         </is>
       </c>
-      <c r="B3" s="11" t="inlineStr">
+      <c r="B3" s="8" t="inlineStr">
         <is>
           <t>INT</t>
         </is>
       </c>
-      <c r="C3" s="11" t="n"/>
-      <c r="D3" s="11" t="n"/>
-      <c r="E3" s="11" t="n"/>
-      <c r="F3" s="11" t="inlineStr">
+      <c r="C3" s="8" t="inlineStr">
+        <is>
+          <t>INT</t>
+        </is>
+      </c>
+      <c r="D3" s="8" t="n"/>
+      <c r="E3" s="8" t="n"/>
+      <c r="F3" s="8" t="inlineStr">
         <is>
           <t>schema_name="analytics_db"; table_name="company_groups"; column_name="INN"; relation_type="ONE_TO_MANY"</t>
         </is>
       </c>
-      <c r="G3" s="12">
+      <c r="G3" s="9">
         <f>IF($F3&lt;&gt;"","Для foreign_key допустим только null_ratio=0..1. Остальные generator constraints запрещены.",IFERROR(VLOOKUP($B3,'Constant List'!$A$2:$B$7,2,FALSE),"Тип данных не заполнен"))</f>
         <v/>
       </c>
-      <c r="H3" s="12">
+      <c r="H3" s="14">
         <f>'Constant List'!$J$2</f>
         <v/>
       </c>
     </row>
-    <row r="4" ht="85.5" customHeight="1" s="8">
-      <c r="A4" s="11" t="inlineStr">
+    <row r="4" ht="85.5" customHeight="1" s="7">
+      <c r="A4" s="13" t="inlineStr">
         <is>
           <t>SOGRN</t>
         </is>
       </c>
-      <c r="B4" s="11" t="inlineStr">
+      <c r="B4" s="8" t="inlineStr">
         <is>
           <t>INT</t>
         </is>
       </c>
-      <c r="C4" s="11" t="n"/>
-      <c r="D4" s="11" t="n"/>
-      <c r="E4" s="11" t="inlineStr">
+      <c r="C4" s="8" t="inlineStr">
+        <is>
+          <t>INT</t>
+        </is>
+      </c>
+      <c r="D4" s="8" t="n"/>
+      <c r="E4" s="8" t="inlineStr">
         <is>
           <t>null_ratio=0.1; min_value=1000000000000; max_value=1000000000000000</t>
         </is>
       </c>
-      <c r="F4" s="11" t="n"/>
-      <c r="G4" s="12">
+      <c r="F4" s="8" t="n"/>
+      <c r="G4" s="9">
         <f>IF($F4&lt;&gt;"","Для foreign_key допустим только null_ratio=0..1. Остальные generator constraints запрещены.",IFERROR(VLOOKUP($B4,'Constant List'!$A$2:$B$7,2,FALSE),"Тип данных не заполнен"))</f>
         <v/>
       </c>
-      <c r="H4" s="12">
+      <c r="H4" s="14">
         <f>'Constant List'!$J$2</f>
         <v/>
       </c>
     </row>
-    <row r="5" ht="128.25" customHeight="1" s="8">
-      <c r="A5" s="11" t="inlineStr">
+    <row r="5" ht="128.25" customHeight="1" s="7">
+      <c r="A5" s="13" t="inlineStr">
         <is>
           <t>SPIN</t>
         </is>
       </c>
-      <c r="B5" s="11" t="inlineStr">
+      <c r="B5" s="8" t="inlineStr">
         <is>
           <t>STRING</t>
         </is>
       </c>
-      <c r="C5" s="11" t="n"/>
-      <c r="D5" s="11" t="n"/>
-      <c r="E5" s="11" t="inlineStr">
+      <c r="C5" s="8" t="inlineStr">
+        <is>
+          <t>STRING</t>
+        </is>
+      </c>
+      <c r="D5" s="8" t="n"/>
+      <c r="E5" s="8" t="inlineStr">
         <is>
           <t>null_ratio=0.1; length=6; case_mode="upper"; regular_expr="^[A-Z0-9]{6}$"</t>
         </is>
       </c>
-      <c r="F5" s="11" t="n"/>
-      <c r="G5" s="12">
+      <c r="F5" s="8" t="n"/>
+      <c r="G5" s="9">
         <f>IF($F5&lt;&gt;"","Для foreign_key допустим только null_ratio=0..1. Остальные generator constraints запрещены.",IFERROR(VLOOKUP($B5,'Constant List'!$A$2:$B$7,2,FALSE),"Тип данных не заполнен"))</f>
         <v/>
       </c>
-      <c r="H5" s="12">
+      <c r="H5" s="14">
         <f>'Constant List'!$J$2</f>
         <v/>
       </c>
     </row>
-    <row r="6" ht="128.25" customHeight="1" s="8">
-      <c r="A6" s="11" t="inlineStr">
+    <row r="6" ht="128.25" customHeight="1" s="7">
+      <c r="A6" s="13" t="inlineStr">
         <is>
           <t>SABSCODE</t>
         </is>
       </c>
-      <c r="B6" s="11" t="inlineStr">
+      <c r="B6" s="8" t="inlineStr">
         <is>
           <t>STRING</t>
         </is>
       </c>
-      <c r="C6" s="11" t="n"/>
-      <c r="D6" s="11" t="n"/>
-      <c r="E6" s="11" t="inlineStr">
+      <c r="C6" s="8" t="inlineStr">
+        <is>
+          <t>STRING</t>
+        </is>
+      </c>
+      <c r="D6" s="8" t="n"/>
+      <c r="E6" s="8" t="inlineStr">
         <is>
           <t>allowed_values=["SFAProd"]</t>
         </is>
       </c>
-      <c r="F6" s="11" t="n"/>
-      <c r="G6" s="12">
+      <c r="F6" s="8" t="n"/>
+      <c r="G6" s="9">
         <f>IF($F6&lt;&gt;"","Для foreign_key допустим только null_ratio=0..1. Остальные generator constraints запрещены.",IFERROR(VLOOKUP($B6,'Constant List'!$A$2:$B$7,2,FALSE),"Тип данных не заполнен"))</f>
         <v/>
       </c>
-      <c r="H6" s="12">
+      <c r="H6" s="14">
         <f>'Constant List'!$J$2</f>
         <v/>
       </c>
     </row>
-    <row r="7" ht="128.25" customHeight="1" s="8">
-      <c r="A7" s="11" t="inlineStr">
+    <row r="7" ht="128.25" customHeight="1" s="7">
+      <c r="A7" s="13" t="inlineStr">
         <is>
           <t>SPINSFA</t>
         </is>
       </c>
-      <c r="B7" s="11" t="inlineStr">
+      <c r="B7" s="8" t="inlineStr">
         <is>
           <t>STRING</t>
         </is>
       </c>
-      <c r="C7" s="11" t="n"/>
-      <c r="D7" s="11" t="n"/>
-      <c r="E7" s="11" t="inlineStr">
+      <c r="C7" s="8" t="inlineStr">
+        <is>
+          <t>STRING</t>
+        </is>
+      </c>
+      <c r="D7" s="8" t="n"/>
+      <c r="E7" s="8" t="inlineStr">
         <is>
           <t>regular_expr="^ABR-FW-SCRMFW-WORK-ACCOUNT ACB-\d+$"</t>
         </is>
       </c>
-      <c r="F7" s="11" t="n"/>
-      <c r="G7" s="12">
+      <c r="F7" s="8" t="n"/>
+      <c r="G7" s="9">
         <f>IF($F7&lt;&gt;"","Для foreign_key допустим только null_ratio=0..1. Остальные generator constraints запрещены.",IFERROR(VLOOKUP($B7,'Constant List'!$A$2:$B$7,2,FALSE),"Тип данных не заполнен"))</f>
         <v/>
       </c>
-      <c r="H7" s="12">
+      <c r="H7" s="14">
         <f>'Constant List'!$J$2</f>
         <v/>
       </c>
     </row>
-    <row r="8" ht="85.5" customHeight="1" s="8">
-      <c r="A8" s="11" t="inlineStr">
+    <row r="8" ht="85.5" customHeight="1" s="7">
+      <c r="A8" s="19" t="inlineStr">
         <is>
           <t>IDSUBJECT</t>
         </is>
       </c>
-      <c r="B8" s="11" t="inlineStr">
+      <c r="B8" s="20" t="inlineStr">
         <is>
           <t>INT</t>
         </is>
       </c>
-      <c r="C8" s="11" t="n"/>
-      <c r="D8" s="11" t="n"/>
-      <c r="E8" s="11" t="inlineStr">
+      <c r="C8" s="20" t="inlineStr">
+        <is>
+          <t>INT</t>
+        </is>
+      </c>
+      <c r="D8" s="20" t="n"/>
+      <c r="E8" s="20" t="inlineStr">
         <is>
           <t>min_value=1; max_value=20000000</t>
         </is>
       </c>
-      <c r="F8" s="11" t="n"/>
-      <c r="G8" s="12">
+      <c r="F8" s="20" t="n"/>
+      <c r="G8" s="21">
         <f>IF($F8&lt;&gt;"","Для foreign_key допустим только null_ratio=0..1. Остальные generator constraints запрещены.",IFERROR(VLOOKUP($B8,'Constant List'!$A$2:$B$7,2,FALSE),"Тип данных не заполнен"))</f>
         <v/>
       </c>
-      <c r="H8" s="12">
+      <c r="H8" s="22">
         <f>'Constant List'!$J$2</f>
         <v/>
       </c>
@@ -2058,5 +2837,8 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>
--- a/datagen/params/data_gen.xlsx
+++ b/datagen/params/data_gen.xlsx
@@ -1398,7 +1398,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>В листе таблицы обязательны column_name и gen_data_type; output_data_type можно оставить пустым.</t>
+          <t>В листе таблицы обязательны только column_name и gen_data_type. output_data_type, is_primary_key, constraints и foreign_key можно не заполнять.</t>
         </is>
       </c>
     </row>
@@ -1446,7 +1446,7 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>Для foreign_key допустим только null_ratio; остальные generator constraints запрещены.</t>
+          <t>Для foreign_key из constraints допустим только null_ratio; если constraints пусто, используется default null_ratio=0.</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>Для primary key обязателен null_ratio=0.</t>
+          <t>Для primary key не нужно указывать null_ratio и is_unique: система сама применяет null_ratio=0 и is_unique=true.</t>
         </is>
       </c>
     </row>
@@ -1491,7 +1491,7 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>Имя итоговой колонки в таблице.</t>
+          <t>Обязательное поле. Имя итоговой колонки в таблице.</t>
         </is>
       </c>
     </row>
@@ -1503,7 +1503,7 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>Исходный тип генератора: STRING, INT, FLOAT, DATE, TIMESTAMP, BOOLEAN.</t>
+          <t>Обязательное поле. Исходный тип генератора: STRING, INT, FLOAT, DATE, TIMESTAMP, BOOLEAN.</t>
         </is>
       </c>
     </row>
@@ -1515,7 +1515,7 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>Финальный тип после конвертации; если пусто, результат остается в gen_data_type.</t>
+          <t>Опционально. Если пусто, используется gen_data_type; исключение: DATE/TIMESTAMP с date_format/timestamp_format по умолчанию выводятся как STRING.</t>
         </is>
       </c>
     </row>
@@ -1527,7 +1527,7 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>TRUE если колонка первичный ключ; тогда значение должно быть уникальным и null_ratio обязан быть 0.</t>
+          <t>Опционально. TRUE если колонка primary key; тогда система сама ставит is_unique=true и null_ratio=0.</t>
         </is>
       </c>
     </row>
@@ -1539,7 +1539,7 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>Одна строка key=value; key=value с ограничениями для выбранного gen_data_type.</t>
+          <t>Опционально. Одна строка key=value; key=value. Если пусто, применяются дефолты выбранного типа и output constraints.</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>Одна строка key=value; key=value со ссылкой на родительскую колонку.</t>
+          <t>Опционально. Одна строка key=value; key=value со ссылкой на родительскую колонку.</t>
         </is>
       </c>
     </row>
@@ -1572,7 +1572,7 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>Доля NULL в итоговых данных от 0 до 1.</t>
+          <t>Опционально. Доля NULL в итоговых данных от 0 до 1; default = 0.</t>
         </is>
       </c>
     </row>
@@ -1584,7 +1584,7 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>Требует уникальные итоговые значения после всех конвертаций.</t>
+          <t>Опционально. Требует уникальные итоговые значения после всех конвертаций; default = false. Не нужно указывать для primary key.</t>
         </is>
       </c>
     </row>
@@ -1596,7 +1596,7 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>Ограничивает генерацию только указанным списком значений; задается только JSON-массивом.</t>
+          <t>Опционально. Ограничивает генерацию только указанным JSON-массивом значений.</t>
         </is>
       </c>
     </row>
@@ -1617,7 +1617,7 @@
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>Фиксированная длина строки.</t>
+          <t>Опционально. Фиксированная длина строки; default = 10.</t>
         </is>
       </c>
     </row>
@@ -1629,7 +1629,7 @@
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>Набор символов: letters = только буквы, digits = только цифры, alphanumeric = буквы и цифры.</t>
+          <t>Опционально. Набор символов: letters, digits, alphanumeric; default = letters.</t>
         </is>
       </c>
     </row>
@@ -1641,7 +1641,7 @@
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>Регистр строки: mixed = смешанный регистр, lower = только нижний регистр, upper = только верхний регистр.</t>
+          <t>Опционально. Регистр строки: mixed, lower, upper; default = mixed.</t>
         </is>
       </c>
     </row>
@@ -1674,7 +1674,7 @@
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>Минимальное числовое значение для INT или FLOAT.</t>
+          <t>Опционально. Минимальное числовое значение для INT или FLOAT; default = 0.</t>
         </is>
       </c>
     </row>
@@ -1686,7 +1686,7 @@
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>Максимальное числовое значение для INT или FLOAT.</t>
+          <t>Опционально. Максимальное числовое значение для INT или FLOAT; default = 1000.</t>
         </is>
       </c>
     </row>
@@ -1698,11 +1698,22 @@
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>Количество знаков после запятой; используется только для FLOAT.</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="10.05" customHeight="1" s="7"/>
+          <t>Опционально. Количество знаков после запятой; используется только для FLOAT; default = 2.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="22.05" customHeight="1" s="7">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>digits_count</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>Опционально только для INT. Задает точную длину числа в цифрах; нельзя вместе с min_value, max_value, allowed_values.</t>
+        </is>
+      </c>
+    </row>
     <row r="37" ht="24" customHeight="1" s="7">
       <c r="A37" s="6" t="inlineStr">
         <is>
@@ -1719,7 +1730,7 @@
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>Минимальная дата; задается строкой, которую можно распарсить как дату.</t>
+          <t>Опционально. Минимальная дата; default = 1 января текущего года.</t>
         </is>
       </c>
     </row>
@@ -1731,7 +1742,7 @@
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>Максимальная дата; задается строкой, которую можно распарсить как дату.</t>
+          <t>Опционально. Максимальная дата; default = 31 декабря текущего года.</t>
         </is>
       </c>
     </row>
@@ -1743,7 +1754,7 @@
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>Формат текстового вывода даты, например %Y-%m-%d; обычно используется вместе с output_data_type=STRING.</t>
+          <t>Опционально. Формат текстового вывода даты; default = %Y-%m-%d. Если output_data_type пустой и указан date_format, output становится STRING.</t>
         </is>
       </c>
     </row>
@@ -1764,7 +1775,7 @@
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>Минимальный timestamp в формате строки, например 2024-01-01 00:00:00.</t>
+          <t>Опционально. Минимальный timestamp; default = 1 января текущего года 00:00:00.</t>
         </is>
       </c>
     </row>
@@ -1776,7 +1787,7 @@
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>Максимальный timestamp в формате строки, например 2024-12-31 23:59:59.</t>
+          <t>Опционально. Максимальный timestamp; default = 31 декабря текущего года 23:59:59.</t>
         </is>
       </c>
     </row>
@@ -1788,7 +1799,7 @@
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>Формат текстового вывода timestamp, например %Y-%m-%d %H:%M:%S.</t>
+          <t>Опционально. Формат текстового вывода timestamp; default = %Y-%m-%d %H:%M:%S. Если output_data_type пустой и указан timestamp_format, output становится STRING.</t>
         </is>
       </c>
     </row>
@@ -1809,7 +1820,7 @@
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>Обычно [true, false], но можно ограничить, например, только [true].</t>
+          <t>Опционально. Обычно [true, false], но можно ограничить, например, только [true].</t>
         </is>
       </c>
     </row>
@@ -1854,7 +1865,7 @@
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>Если указан foreign_key, из generator constraints допустим только null_ratio.</t>
+          <t>Если указан foreign_key, из constraints допустим только null_ratio; default для foreign key = 0.</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2694,7 @@
       <c r="D4" s="8" t="n"/>
       <c r="E4" s="8" t="inlineStr">
         <is>
-          <t>null_ratio=0.1; min_value=1000000000000; max_value=1000000000000000</t>
+          <t>null_ratio=0.1; min_value=1000000000000; max_value=999999999999999</t>
         </is>
       </c>
       <c r="F4" s="8" t="n"/>
@@ -2779,7 +2790,7 @@
       <c r="D7" s="8" t="n"/>
       <c r="E7" s="8" t="inlineStr">
         <is>
-          <t>regular_expr="^ABR-FW-SCRMFW-WORK-ACCOUNT ACB-\d+$"</t>
+          <t>regular_expr="^ABR-FW-SCRMFW-WORK-ACCOUNT ACB-[0-9]{1,20}$"</t>
         </is>
       </c>
       <c r="F7" s="8" t="n"/>

--- a/datagen/params/data_gen.xlsx
+++ b/datagen/params/data_gen.xlsx
@@ -9,8 +9,9 @@
     <sheet name="Инструкция" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Constant List" sheetId="2" state="hidden" r:id="rId2"/>
     <sheet name="tables" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="analytics_db.company_groups" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="analytics_db.subjects" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="queries" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="company_groups" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="subjects" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="BOOL_VALUES">'Constant List'!$H$2:$H$3</definedName>
@@ -21,6 +22,10 @@
     <definedName name="OUTPUT_TYPES_INT">'Constant List'!$N$2:$N$5</definedName>
     <definedName name="OUTPUT_TYPES_STRING">'Constant List'!$M$2:$M$3</definedName>
     <definedName name="OUTPUT_TYPES_TIMESTAMP">'Constant List'!$Q$2:$Q$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'tables'!$A$1:$G$200</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'queries'!$A$1:$D$20</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'company_groups'!$A$1:$K$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'subjects'!$A$1:$K$8</definedName>
   </definedNames>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
@@ -301,7 +306,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -363,6 +368,12 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="7" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1017,48 +1028,6 @@
     </indexedColors>
   </colors>
 </styleSheet>
-</file>
-
-<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Таблица1" displayName="Таблица1" ref="A1:H5" headerRowCount="1" totalsRowShown="0" headerRowDxfId="13" dataDxfId="14" headerRowBorderDxfId="24" tableBorderDxfId="25" totalsRowBorderDxfId="23">
-  <autoFilter ref="A1:H5"/>
-  <tableColumns count="8">
-    <tableColumn id="1" name="column_name" dataDxfId="22"/>
-    <tableColumn id="2" name="gen_data_type" dataDxfId="21"/>
-    <tableColumn id="3" name="output_data_type" dataDxfId="20"/>
-    <tableColumn id="4" name="is_primary_key" dataDxfId="19"/>
-    <tableColumn id="5" name="constraints" dataDxfId="18"/>
-    <tableColumn id="6" name="foreign_key" dataDxfId="17"/>
-    <tableColumn id="7" name="Подсказка по constraints" dataDxfId="16">
-      <calculatedColumnFormula>IF($F2&lt;&gt;"","Для foreign_key допустим только null_ratio=0..1. Остальные generator constraints запрещены.",IFERROR(VLOOKUP($B2,'Constant List'!$A$2:$B$7,2,FALSE),"Тип данных не заполнен"))</calculatedColumnFormula>
-    </tableColumn>
-    <tableColumn id="8" name="Пример заполнения foreign_key" dataDxfId="15">
-      <calculatedColumnFormula>'Constant List'!$J$2</calculatedColumnFormula>
-    </tableColumn>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
-<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Таблица2" displayName="Таблица2" ref="A1:H8" headerRowCount="1" totalsRowShown="0" headerRowDxfId="0" dataDxfId="1" headerRowBorderDxfId="11" tableBorderDxfId="12" totalsRowBorderDxfId="10">
-  <autoFilter ref="A1:H8"/>
-  <tableColumns count="8">
-    <tableColumn id="1" name="column_name" dataDxfId="9"/>
-    <tableColumn id="2" name="gen_data_type" dataDxfId="8"/>
-    <tableColumn id="3" name="output_data_type" dataDxfId="7"/>
-    <tableColumn id="4" name="is_primary_key" dataDxfId="6"/>
-    <tableColumn id="5" name="constraints" dataDxfId="5"/>
-    <tableColumn id="6" name="foreign_key" dataDxfId="4"/>
-    <tableColumn id="7" name="Подсказка по constraints" dataDxfId="3">
-      <calculatedColumnFormula>IF($F2&lt;&gt;"","Для foreign_key допустим только null_ratio=0..1. Остальные generator constraints запрещены.",IFERROR(VLOOKUP($B2,'Constant List'!$A$2:$B$7,2,FALSE),"Тип данных не заполнен"))</calculatedColumnFormula>
-    </tableColumn>
-    <tableColumn id="8" name="Пример заполнения foreign_key" dataDxfId="2">
-      <calculatedColumnFormula>'Constant List'!$J$2</calculatedColumnFormula>
-    </tableColumn>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1350,23 +1319,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B61"/>
+  <dimension ref="A1:B45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.25"/>
   <cols>
-    <col width="34" customWidth="1" style="7" min="1" max="1"/>
-    <col width="120" customWidth="1" style="7" min="2" max="2"/>
+    <col width="28" customWidth="1" style="7" min="1" max="1"/>
+    <col width="115" customWidth="1" style="7" min="2" max="2"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1" s="7">
+    <row r="1" ht="30" customHeight="1" s="7">
       <c r="A1" s="11" t="inlineStr">
         <is>
-          <t>Шаблон DataGen: как заполнять Excel</t>
+          <t>Шаблон DataGen: existing Hive/Iceberg tables + compare queries</t>
         </is>
       </c>
       <c r="B1" s="12" t="n"/>
     </row>
-    <row r="2" ht="10.05" customHeight="1" s="7"/>
-    <row r="3" ht="22.05" customHeight="1" s="7">
+    <row r="2" ht="8" customHeight="1" s="7"/>
+    <row r="3" ht="44" customHeight="1" s="7">
       <c r="A3" s="4" t="inlineStr">
         <is>
           <t>Шаг 1</t>
@@ -1374,11 +1343,11 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>На листе tables заполните schema_name, table_name и total_rows.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="22.05" customHeight="1" s="7">
+          <t>На листе tables заполните table_name, total_rows, явные target tables, общий write_mode и partition columns по каждому engine.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="26" customHeight="1" s="7">
       <c r="A4" s="4" t="inlineStr">
         <is>
           <t>Шаг 2</t>
@@ -1386,11 +1355,11 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>Для каждой строки из tables используйте отдельный лист с именем schema.table.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="30" customHeight="1" s="7">
+          <t>Для каждой строки из tables используйте отдельный лист с именем table_name.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="44" customHeight="1" s="7">
       <c r="A5" s="4" t="inlineStr">
         <is>
           <t>Шаг 3</t>
@@ -1398,11 +1367,11 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>В листе таблицы обязательны только column_name и gen_data_type. output_data_type, is_primary_key, constraints и foreign_key можно не заполнять.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="22.05" customHeight="1" s="7">
+          <t>На листе queries укажите ровно два SQL: hive_sql и iceberg_sql. Сравниваются только результаты этих запросов.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="44" customHeight="1" s="7">
       <c r="A6" s="4" t="inlineStr">
         <is>
           <t>Шаг 4</t>
@@ -1410,11 +1379,11 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>constraints заполняется одной строкой в формате key=value; key=value.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="22.05" customHeight="1" s="7">
+          <t>Если поле есть только в одном engine, не возвращайте его в compare SQL. Такие поля могут жить в parquet, но не должны участвовать в сверке.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="44" customHeight="1" s="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
           <t>Шаг 5</t>
@@ -1422,11 +1391,11 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>allowed_values всегда задается JSON-массивом: ["A", "B"], [1, 2], [true, false].</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="22.05" customHeight="1" s="7">
+          <t>DATE/TIMESTAMP колонки из результата compare автоматически исключаются перед нормализацией. Если нужно сравнивать день или месяц, приводите его в SQL к INT или STRING.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="44" customHeight="1" s="7">
       <c r="A8" s="4" t="inlineStr">
         <is>
           <t>Шаг 6</t>
@@ -1434,11 +1403,11 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>foreign_key тоже задается одной строкой key=value; key=value.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="30" customHeight="1" s="7">
+          <t>Дополнительные поля ignore в queries задаются строкой через запятую: alias1, alias2, alias3. Они расширяют built-in ignore словарь техполей для engine.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="44" customHeight="1" s="7">
       <c r="A9" s="4" t="inlineStr">
         <is>
           <t>Шаг 7</t>
@@ -1446,11 +1415,11 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>Для foreign_key из constraints допустим только null_ratio; если constraints пусто, используется default null_ratio=0.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="22.05" customHeight="1" s="7">
+          <t>В sheet таблицы каждая строка должна быть ровно одного типа: generated, foreign key или derived.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="44" customHeight="1" s="7">
       <c r="A10" s="4" t="inlineStr">
         <is>
           <t>Шаг 8</t>
@@ -1458,11 +1427,11 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>Для primary key не нужно указывать null_ratio и is_unique: система сама применяет null_ratio=0 и is_unique=true.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="30" customHeight="1" s="7">
+          <t>generated: заполнены column_name + gen_data_type. output_data_type опционален, остальные специальные поля пустые.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="44" customHeight="1" s="7">
       <c r="A11" s="4" t="inlineStr">
         <is>
           <t>Шаг 9</t>
@@ -1470,486 +1439,374 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>output_data_type выбирается только из допустимого dropdown по выбранному gen_data_type.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="10.05" customHeight="1" s="7"/>
-    <row r="13" ht="24" customHeight="1" s="7">
-      <c r="A13" s="6" t="inlineStr">
-        <is>
-          <t>Общие колонки</t>
-        </is>
-      </c>
-      <c r="B13" s="6" t="n"/>
-    </row>
-    <row r="14" ht="22.05" customHeight="1" s="7">
+          <t>foreign key: заполнен только foreign_key. gen_data_type и output_data_type не указываются вручную, constraints допускает только null_ratio.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="44" customHeight="1" s="7">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>Шаг 10</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>derived: заполнены derive + output_data_type. gen_data_type, constraints и foreign_key остаются пустыми.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="44" customHeight="1" s="7">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>Шаг 11</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>engine_scope: both по умолчанию. hive_only и iceberg_only используйте только для колонок, которые реально нужны одному движку.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="44" customHeight="1" s="7">
       <c r="A14" s="4" t="inlineStr">
         <is>
+          <t>Шаг 12</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>Если target column нет в parquet: nullable -&gt; loader ставит NULL; non-nullable -&gt; загрузка падает. Broad autofill по type defaults в v1 не используется.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="8" customHeight="1" s="7"/>
+    <row r="16" ht="24" customHeight="1" s="7">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>Колонки листа tables</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="n"/>
+    </row>
+    <row r="17" ht="44" customHeight="1" s="7">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>table_name</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>Обязательное поле. Логическое имя таблицы в DataGen и имя sheet. Должно быть уникальным в workbook.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="26" customHeight="1" s="7">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>total_rows</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>Обязательное поле. Количество строк для генерации.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="26" customHeight="1" s="7">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>hive_target_table</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>Обязательное поле. Полное имя существующей Hive-таблицы.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="26" customHeight="1" s="7">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>iceberg_target_table</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>Обязательное поле. Полное имя существующей Iceberg-таблицы.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="44" customHeight="1" s="7">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>write_mode</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>Обязательное поле. Один общий режим записи: OVERWRITE_TABLE, OVERWRITE_PARTITIONS, APPEND.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="44" customHeight="1" s="7">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>hive_partition_columns</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>Опционально. Список partition columns через запятую для Hive. Обязателен только для OVERWRITE_PARTITIONS.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="44" customHeight="1" s="7">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>iceberg_partition_columns</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>Опционально. Список partition columns через запятую для Iceberg. Обязателен только для OVERWRITE_PARTITIONS.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="8" customHeight="1" s="7"/>
+    <row r="25" ht="24" customHeight="1" s="7">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>Колонки листа table_name</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="n"/>
+    </row>
+    <row r="26" ht="26" customHeight="1" s="7">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
           <t>column_name</t>
         </is>
       </c>
-      <c r="B14" s="5" t="inlineStr">
-        <is>
-          <t>Обязательное поле. Имя итоговой колонки в таблице.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="22.05" customHeight="1" s="7">
-      <c r="A15" s="4" t="inlineStr">
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>Обязательное поле. Имя итоговой колонки в parquet и/или target table.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="44" customHeight="1" s="7">
+      <c r="A27" s="4" t="inlineStr">
         <is>
           <t>gen_data_type</t>
         </is>
       </c>
-      <c r="B15" s="5" t="inlineStr">
-        <is>
-          <t>Обязательное поле. Исходный тип генератора: STRING, INT, FLOAT, DATE, TIMESTAMP, BOOLEAN.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="22.05" customHeight="1" s="7">
-      <c r="A16" s="4" t="inlineStr">
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>Обязательное только для generated-колонки. STRING, INT, FLOAT, DATE, TIMESTAMP, BOOLEAN.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="26" customHeight="1" s="7">
+      <c r="A28" s="4" t="inlineStr">
         <is>
           <t>output_data_type</t>
         </is>
       </c>
-      <c r="B16" s="5" t="inlineStr">
-        <is>
-          <t>Опционально. Если пусто, используется gen_data_type; исключение: DATE/TIMESTAMP с date_format/timestamp_format по умолчанию выводятся как STRING.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="30" customHeight="1" s="7">
-      <c r="A17" s="4" t="inlineStr">
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t>Опционально для generated, обязательно для derived, пусто для foreign key.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="44" customHeight="1" s="7">
+      <c r="A29" s="4" t="inlineStr">
         <is>
           <t>is_primary_key</t>
         </is>
       </c>
-      <c r="B17" s="5" t="inlineStr">
-        <is>
-          <t>Опционально. TRUE если колонка primary key; тогда система сама ставит is_unique=true и null_ratio=0.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="22.05" customHeight="1" s="7">
-      <c r="A18" s="4" t="inlineStr">
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>Опционально. TRUE только для generated-колонок. Для PK система сама применяет null_ratio=0 и is_unique=true.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="44" customHeight="1" s="7">
+      <c r="A30" s="4" t="inlineStr">
         <is>
           <t>constraints</t>
         </is>
       </c>
-      <c r="B18" s="5" t="inlineStr">
-        <is>
-          <t>Опционально. Одна строка key=value; key=value. Если пусто, применяются дефолты выбранного типа и output constraints.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="22.05" customHeight="1" s="7">
-      <c r="A19" s="4" t="inlineStr">
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>Опционально только для generated. Формат key=value; key=value. Для foreign key допустим только null_ratio, для derived поле должно быть пустым.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="44" customHeight="1" s="7">
+      <c r="A31" s="4" t="inlineStr">
         <is>
           <t>foreign_key</t>
         </is>
       </c>
-      <c r="B19" s="5" t="inlineStr">
-        <is>
-          <t>Опционально. Одна строка key=value; key=value со ссылкой на родительскую колонку.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="10.05" customHeight="1" s="7"/>
-    <row r="21" ht="24" customHeight="1" s="7">
-      <c r="A21" s="6" t="inlineStr">
-        <is>
-          <t>Общие constraints</t>
-        </is>
-      </c>
-      <c r="B21" s="6" t="n"/>
-    </row>
-    <row r="22" ht="22.05" customHeight="1" s="7">
-      <c r="A22" s="4" t="inlineStr">
-        <is>
-          <t>null_ratio</t>
-        </is>
-      </c>
-      <c r="B22" s="5" t="inlineStr">
-        <is>
-          <t>Опционально. Доля NULL в итоговых данных от 0 до 1; default = 0.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="22.05" customHeight="1" s="7">
-      <c r="A23" s="4" t="inlineStr">
-        <is>
-          <t>is_unique</t>
-        </is>
-      </c>
-      <c r="B23" s="5" t="inlineStr">
-        <is>
-          <t>Опционально. Требует уникальные итоговые значения после всех конвертаций; default = false. Не нужно указывать для primary key.</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="30" customHeight="1" s="7">
-      <c r="A24" s="4" t="inlineStr">
-        <is>
-          <t>allowed_values</t>
-        </is>
-      </c>
-      <c r="B24" s="5" t="inlineStr">
-        <is>
-          <t>Опционально. Ограничивает генерацию только указанным JSON-массивом значений.</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="10.05" customHeight="1" s="7"/>
-    <row r="26" ht="24" customHeight="1" s="7">
-      <c r="A26" s="6" t="inlineStr">
-        <is>
-          <t>STRING constraints</t>
-        </is>
-      </c>
-      <c r="B26" s="6" t="n"/>
-    </row>
-    <row r="27" ht="22.05" customHeight="1" s="7">
-      <c r="A27" s="4" t="inlineStr">
-        <is>
-          <t>length</t>
-        </is>
-      </c>
-      <c r="B27" s="5" t="inlineStr">
-        <is>
-          <t>Опционально. Фиксированная длина строки; default = 10.</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="30" customHeight="1" s="7">
-      <c r="A28" s="4" t="inlineStr">
-        <is>
-          <t>character_set</t>
-        </is>
-      </c>
-      <c r="B28" s="5" t="inlineStr">
-        <is>
-          <t>Опционально. Набор символов: letters, digits, alphanumeric; default = letters.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="30" customHeight="1" s="7">
-      <c r="A29" s="4" t="inlineStr">
-        <is>
-          <t>case_mode</t>
-        </is>
-      </c>
-      <c r="B29" s="5" t="inlineStr">
-        <is>
-          <t>Опционально. Регистр строки: mixed, lower, upper; default = mixed.</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="22.05" customHeight="1" s="7">
-      <c r="A30" s="4" t="inlineStr">
-        <is>
-          <t>regular_expr</t>
-        </is>
-      </c>
-      <c r="B30" s="5" t="inlineStr">
-        <is>
-          <t>Regex-шаблон, которому должна соответствовать строка.</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="10.05" customHeight="1" s="7"/>
-    <row r="32" ht="24" customHeight="1" s="7">
-      <c r="A32" s="6" t="inlineStr">
-        <is>
-          <t>INT / FLOAT constraints</t>
-        </is>
-      </c>
-      <c r="B32" s="6" t="n"/>
-    </row>
-    <row r="33" ht="22.05" customHeight="1" s="7">
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>Формат: table_name="..."; column_name="..."; relation_type="ONE_TO_MANY|ONE_TO_ONE".</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="26" customHeight="1" s="7">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>engine_scope</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>Опционально. both | hive_only | iceberg_only. Если пусто, трактуется как both.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="44" customHeight="1" s="7">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>min_value</t>
+          <t>derive</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>Опционально. Минимальное числовое значение для INT или FLOAT; default = 0.</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="22.05" customHeight="1" s="7">
-      <c r="A34" s="4" t="inlineStr">
-        <is>
-          <t>max_value</t>
-        </is>
-      </c>
-      <c r="B34" s="5" t="inlineStr">
-        <is>
-          <t>Опционально. Максимальное числовое значение для INT или FLOAT; default = 1000.</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="22.05" customHeight="1" s="7">
-      <c r="A35" s="4" t="inlineStr">
-        <is>
-          <t>precision</t>
-        </is>
-      </c>
-      <c r="B35" s="5" t="inlineStr">
-        <is>
-          <t>Опционально. Количество знаков после запятой; используется только для FLOAT; default = 2.</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="22.05" customHeight="1" s="7">
+          <t>Формат: source_column="VALUE_DAY"; rule="YYYYMMDD". Используется только для derived-колонок.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="8" customHeight="1" s="7"/>
+    <row r="35" ht="24" customHeight="1" s="7">
+      <c r="A35" s="6" t="inlineStr">
+        <is>
+          <t>Колонки листа queries</t>
+        </is>
+      </c>
+      <c r="B35" s="6" t="n"/>
+    </row>
+    <row r="36" ht="26" customHeight="1" s="7">
       <c r="A36" s="4" t="inlineStr">
         <is>
-          <t>digits_count</t>
+          <t>hive_sql</t>
         </is>
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>Опционально только для INT. Задает точную длину числа в цифрах; нельзя вместе с min_value, max_value, allowed_values.</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="24" customHeight="1" s="7">
-      <c r="A37" s="6" t="inlineStr">
-        <is>
-          <t>DATE constraints</t>
-        </is>
-      </c>
-      <c r="B37" s="6" t="n"/>
-    </row>
-    <row r="38" ht="22.05" customHeight="1" s="7">
+          <t>Обязательное поле. Hive SQL, который возвращает только сравнимые result columns.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="26" customHeight="1" s="7">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>iceberg_sql</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="inlineStr">
+        <is>
+          <t>Обязательное поле. Iceberg SQL с той же бизнес-семантикой, что и hive_sql.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="44" customHeight="1" s="7">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t>min_value</t>
+          <t>hive_exclude_columns</t>
         </is>
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>Опционально. Минимальная дата; default = 1 января текущего года.</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="22.05" customHeight="1" s="7">
+          <t>Опционально. Дополнительные alias-колонки через запятую, которые нужно исключить из compare результата Hive.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="44" customHeight="1" s="7">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>max_value</t>
+          <t>iceberg_exclude_columns</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>Опционально. Максимальная дата; default = 31 декабря текущего года.</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="30" customHeight="1" s="7">
-      <c r="A40" s="4" t="inlineStr">
-        <is>
-          <t>date_format</t>
-        </is>
-      </c>
-      <c r="B40" s="5" t="inlineStr">
-        <is>
-          <t>Опционально. Формат текстового вывода даты; default = %Y-%m-%d. Если output_data_type пустой и указан date_format, output становится STRING.</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="10.05" customHeight="1" s="7"/>
-    <row r="42" ht="24" customHeight="1" s="7">
-      <c r="A42" s="6" t="inlineStr">
-        <is>
-          <t>TIMESTAMP constraints</t>
-        </is>
-      </c>
-      <c r="B42" s="6" t="n"/>
-    </row>
-    <row r="43" ht="22.05" customHeight="1" s="7">
+          <t>Опционально. Дополнительные alias-колонки через запятую, которые нужно исключить из compare результата Iceberg.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="8" customHeight="1" s="7"/>
+    <row r="41" ht="24" customHeight="1" s="7">
+      <c r="A41" s="6" t="inlineStr">
+        <is>
+          <t>Corner cases</t>
+        </is>
+      </c>
+      <c r="B41" s="6" t="n"/>
+    </row>
+    <row r="42" ht="26" customHeight="1" s="7">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>foreign_key + derive</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="inlineStr">
+        <is>
+          <t>Одновременно запрещены.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="44" customHeight="1" s="7">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>min_timestamp</t>
+          <t>derived from derived</t>
         </is>
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>Опционально. Минимальный timestamp; default = 1 января текущего года 00:00:00.</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="22.05" customHeight="1" s="7">
+          <t>Для v1 лучше не использовать. source_column должен ссылаться на обычную или FK-колонку этой же таблицы.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="44" customHeight="1" s="7">
       <c r="A44" s="4" t="inlineStr">
         <is>
-          <t>max_timestamp</t>
+          <t>partition columns</t>
         </is>
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>Опционально. Максимальный timestamp; default = 31 декабря текущего года 23:59:59.</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="22.05" customHeight="1" s="7">
+          <t>Для APPEND и OVERWRITE_TABLE могут быть пустыми. Для OVERWRITE_PARTITIONS обязаны быть заполнены отдельно по каждому engine.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="44" customHeight="1" s="7">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t>timestamp_format</t>
+          <t>query compare</t>
         </is>
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>Опционально. Формат текстового вывода timestamp; default = %Y-%m-%d %H:%M:%S. Если output_data_type пустой и указан timestamp_format, output становится STRING.</t>
+          <t>После ignore и удаления DATE/TIMESTAMP схемы query results должны совпадать. Иначе compare падает.</t>
         </is>
       </c>
     </row>
     <row r="46" ht="10.05" customHeight="1" s="7"/>
-    <row r="47" ht="24" customHeight="1" s="7">
-      <c r="A47" s="6" t="inlineStr">
-        <is>
-          <t>BOOLEAN constraints</t>
-        </is>
-      </c>
-      <c r="B47" s="6" t="n"/>
-    </row>
-    <row r="48" ht="22.05" customHeight="1" s="7">
-      <c r="A48" s="4" t="inlineStr">
-        <is>
-          <t>allowed_values</t>
-        </is>
-      </c>
-      <c r="B48" s="5" t="inlineStr">
-        <is>
-          <t>Опционально. Обычно [true, false], но можно ограничить, например, только [true].</t>
-        </is>
-      </c>
-    </row>
+    <row r="47" ht="24" customHeight="1" s="7"/>
+    <row r="48" ht="22.05" customHeight="1" s="7"/>
     <row r="49" ht="10.05" customHeight="1" s="7"/>
-    <row r="50" ht="24" customHeight="1" s="7">
-      <c r="A50" s="6" t="inlineStr">
-        <is>
-          <t>Foreign Key</t>
-        </is>
-      </c>
-      <c r="B50" s="6" t="n"/>
-    </row>
-    <row r="51" ht="30" customHeight="1" s="7">
-      <c r="A51" s="4" t="inlineStr">
-        <is>
-          <t>foreign_key</t>
-        </is>
-      </c>
-      <c r="B51" s="5" t="inlineStr">
-        <is>
-          <t>Формат: schema_name="analytics_db"; table_name="company_groups"; column_name="INN"; relation_type="ONE_TO_MANY".</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" ht="36" customHeight="1" s="7">
-      <c r="A52" s="4" t="inlineStr">
-        <is>
-          <t>relation_type</t>
-        </is>
-      </c>
-      <c r="B52" s="5" t="inlineStr">
-        <is>
-          <t>ONE_TO_MANY = много дочерних строк могут ссылаться на одного родителя; ONE_TO_ONE = ссылка должна быть уникальной.</t>
-        </is>
-      </c>
-    </row>
-    <row r="53" ht="22.05" customHeight="1" s="7">
-      <c r="A53" s="4" t="inlineStr">
-        <is>
-          <t>Ограничение</t>
-        </is>
-      </c>
-      <c r="B53" s="5" t="inlineStr">
-        <is>
-          <t>Если указан foreign_key, из constraints допустим только null_ratio; default для foreign key = 0.</t>
-        </is>
-      </c>
-    </row>
+    <row r="50" ht="24" customHeight="1" s="7"/>
+    <row r="51" ht="30" customHeight="1" s="7"/>
+    <row r="52" ht="36" customHeight="1" s="7"/>
+    <row r="53" ht="22.05" customHeight="1" s="7"/>
     <row r="54" ht="10.05" customHeight="1" s="7"/>
-    <row r="55" ht="24" customHeight="1" s="7">
-      <c r="A55" s="6" t="inlineStr">
-        <is>
-          <t>Разрешенные output_data_type</t>
-        </is>
-      </c>
-      <c r="B55" s="6" t="n"/>
-    </row>
-    <row r="56" ht="22.05" customHeight="1" s="7">
-      <c r="A56" s="4" t="inlineStr">
-        <is>
-          <t>STRING</t>
-        </is>
-      </c>
-      <c r="B56" s="5" t="inlineStr">
-        <is>
-          <t>STRING, INT</t>
-        </is>
-      </c>
-    </row>
-    <row r="57" ht="22.05" customHeight="1" s="7">
-      <c r="A57" s="4" t="inlineStr">
-        <is>
-          <t>INT</t>
-        </is>
-      </c>
-      <c r="B57" s="5" t="inlineStr">
-        <is>
-          <t>INT, FLOAT, STRING, BOOLEAN</t>
-        </is>
-      </c>
-    </row>
-    <row r="58" ht="22.05" customHeight="1" s="7">
-      <c r="A58" s="4" t="inlineStr">
-        <is>
-          <t>FLOAT</t>
-        </is>
-      </c>
-      <c r="B58" s="5" t="inlineStr">
-        <is>
-          <t>FLOAT, STRING, INT</t>
-        </is>
-      </c>
-    </row>
-    <row r="59" ht="22.05" customHeight="1" s="7">
-      <c r="A59" s="4" t="inlineStr">
-        <is>
-          <t>DATE</t>
-        </is>
-      </c>
-      <c r="B59" s="5" t="inlineStr">
-        <is>
-          <t>DATE, STRING, INT, TIMESTAMP</t>
-        </is>
-      </c>
-    </row>
-    <row r="60" ht="22.05" customHeight="1" s="7">
-      <c r="A60" s="4" t="inlineStr">
-        <is>
-          <t>TIMESTAMP</t>
-        </is>
-      </c>
-      <c r="B60" s="5" t="inlineStr">
-        <is>
-          <t>TIMESTAMP, STRING, INT, DATE</t>
-        </is>
-      </c>
-    </row>
-    <row r="61" ht="22.05" customHeight="1" s="7">
-      <c r="A61" s="4" t="inlineStr">
-        <is>
-          <t>BOOLEAN</t>
-        </is>
-      </c>
-      <c r="B61" s="5" t="inlineStr">
-        <is>
-          <t>BOOLEAN, STRING, INT</t>
-        </is>
-      </c>
-    </row>
+    <row r="55" ht="24" customHeight="1" s="7"/>
+    <row r="56" ht="22.05" customHeight="1" s="7"/>
+    <row r="57" ht="22.05" customHeight="1" s="7"/>
+    <row r="58" ht="22.05" customHeight="1" s="7"/>
+    <row r="59" ht="22.05" customHeight="1" s="7"/>
+    <row r="60" ht="22.05" customHeight="1" s="7"/>
+    <row r="61" ht="22.05" customHeight="1" s="7"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:B1"/>
@@ -1964,284 +1821,232 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R7"/>
+  <dimension ref="A1:N7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.25"/>
   <cols>
-    <col width="63.265625" customWidth="1" style="7" min="2" max="2"/>
-    <col width="24.06640625" customWidth="1" style="7" min="10" max="10"/>
+    <col width="14" customWidth="1" style="7" min="1" max="1"/>
+    <col width="60" customWidth="1" style="7" min="2" max="2"/>
+    <col width="10" customWidth="1" style="7" min="8" max="8"/>
+    <col width="30" customWidth="1" style="7" min="10" max="10"/>
+    <col width="30" customWidth="1" style="7" min="11" max="11"/>
+    <col width="24" customWidth="1" style="7" min="12" max="12"/>
+    <col width="16" customWidth="1" style="7" min="13" max="13"/>
+    <col width="20" customWidth="1" style="7" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="24" t="inlineStr">
         <is>
           <t>Data Type</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="24" t="inlineStr">
         <is>
           <t>Constraint Hint</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="24" t="inlineStr">
         <is>
           <t>Bool</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="24" t="inlineStr">
         <is>
           <t>Foreign Key Example</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>OUTPUT_TYPES_STRING</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>OUTPUT_TYPES_INT</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>OUTPUT_TYPES_FLOAT</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>OUTPUT_TYPES_DATE</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>OUTPUT_TYPES_TIMESTAMP</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>OUTPUT_TYPES_BOOLEAN</t>
+      <c r="K1" s="24" t="inlineStr">
+        <is>
+          <t>Derive Example</t>
+        </is>
+      </c>
+      <c r="L1" s="24" t="inlineStr">
+        <is>
+          <t>Write Mode</t>
+        </is>
+      </c>
+      <c r="M1" s="24" t="inlineStr">
+        <is>
+          <t>Engine Scope</t>
+        </is>
+      </c>
+      <c r="N1" s="24" t="inlineStr">
+        <is>
+          <t>Derive Rule</t>
         </is>
       </c>
     </row>
     <row r="2" ht="114" customHeight="1" s="7">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="24" t="inlineStr">
         <is>
           <t>STRING</t>
         </is>
       </c>
-      <c r="B2" s="10" t="inlineStr">
-        <is>
-          <t>Формат constraints: 
-null_ratio=0..1; 
-is_unique=true/false; 
-allowed_values=["A", "B"]; 
-length=10; 
-character_set="letters|digits|alphanumeric"; 
-case_mode="mixed|lower|upper"; 
+      <c r="B2" s="24" t="inlineStr">
+        <is>
+          <t>Формат constraints:
+null_ratio=0..1;
+is_unique=true/false;
+allowed_values=["A", "B"];
+length=10;
+character_set="letters|digits|alphanumeric";
+case_mode="mixed|lower|upper";
 regular_expr="^[A-Z0-9]{6}$"</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="H2" s="24" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="J2" s="10" t="inlineStr">
-        <is>
-          <t>schema_name="analytics_db"; 
-table_name="company_groups"; 
-column_name="INN"; 
+      <c r="J2" s="24" t="inlineStr">
+        <is>
+          <t>table_name="company_groups";
+column_name="INN";
 relation_type="ONE_TO_MANY|ONE_TO_ONE"</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>STRING</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
+      <c r="K2" s="24" t="inlineStr">
+        <is>
+          <t>source_column="VALUE_DAY";
+rule="YYYYMMDD"</t>
+        </is>
+      </c>
+      <c r="L2" s="24" t="inlineStr">
+        <is>
+          <t>OVERWRITE_TABLE</t>
+        </is>
+      </c>
+      <c r="M2" s="24" t="inlineStr">
+        <is>
+          <t>both</t>
+        </is>
+      </c>
+      <c r="N2" s="24" t="inlineStr">
+        <is>
+          <t>YYYYMMDD</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="85.5" customHeight="1" s="7">
+      <c r="A3" s="24" t="inlineStr">
         <is>
           <t>INT</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="B3" s="24" t="inlineStr">
+        <is>
+          <t>Формат constraints:
+null_ratio=0..1;
+is_unique=true/false;
+allowed_values=[1, 2, 3];
+min_value=0;
+max_value=1000</t>
+        </is>
+      </c>
+      <c r="H3" s="24" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="L3" s="24" t="inlineStr">
+        <is>
+          <t>OVERWRITE_PARTITIONS</t>
+        </is>
+      </c>
+      <c r="M3" s="24" t="inlineStr">
+        <is>
+          <t>hive_only</t>
+        </is>
+      </c>
+      <c r="N3" s="24" t="inlineStr">
+        <is>
+          <t>YEAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="99.75" customHeight="1" s="7">
+      <c r="A4" s="24" t="inlineStr">
         <is>
           <t>FLOAT</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="B4" s="24" t="inlineStr">
+        <is>
+          <t>Формат constraints:
+null_ratio=0..1;
+is_unique=true/false;
+allowed_values=[10.5, 20.25];
+min_value=0.0;
+max_value=1000.0;
+precision=2</t>
+        </is>
+      </c>
+      <c r="L4" s="24" t="inlineStr">
+        <is>
+          <t>APPEND</t>
+        </is>
+      </c>
+      <c r="M4" s="24" t="inlineStr">
+        <is>
+          <t>iceberg_only</t>
+        </is>
+      </c>
+      <c r="N4" s="24" t="inlineStr">
+        <is>
+          <t>MONTH</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="99.75" customHeight="1" s="7">
+      <c r="A5" s="24" t="inlineStr">
         <is>
           <t>DATE</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="B5" s="24" t="inlineStr">
+        <is>
+          <t>Формат constraints:
+null_ratio=0..1;
+is_unique=true/false;
+allowed_values=["2024-01-01", "2024-01-02"];
+min_value="2024-01-01";
+max_value="2024-12-31";
+date_format="%Y-%m-%d"</t>
+        </is>
+      </c>
+      <c r="L5" s="24" t="n"/>
+      <c r="N5" s="24" t="n"/>
+    </row>
+    <row r="6" ht="99.75" customHeight="1" s="7">
+      <c r="A6" s="24" t="inlineStr">
         <is>
           <t>TIMESTAMP</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="B6" s="24" t="inlineStr">
+        <is>
+          <t>Формат constraints:
+null_ratio=0..1;
+is_unique=true/false;
+allowed_values=["2024-01-01 00:00:00", "2024-01-01 00:01:00"];
+min_timestamp="2024-01-01 00:00:00";
+max_timestamp="2024-12-31 23:59:59";
+timestamp_format="%Y-%m-%d %H:%M:%S"</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="57" customHeight="1" s="7">
+      <c r="A7" s="24" t="inlineStr">
         <is>
           <t>BOOLEAN</t>
         </is>
       </c>
-    </row>
-    <row r="3" ht="85.5" customHeight="1" s="7">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>INT</t>
-        </is>
-      </c>
-      <c r="B3" s="10" t="inlineStr">
-        <is>
-          <t>Формат constraints: 
-null_ratio=0..1; 
-is_unique=true/false; 
-allowed_values=[1, 2, 3];
-min_value=0; 
-max_value=1000</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>FALSE</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>INT</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>FLOAT</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>STRING</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>STRING</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>STRING</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>STRING</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="99.75" customHeight="1" s="7">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>FLOAT</t>
-        </is>
-      </c>
-      <c r="B4" s="10" t="inlineStr">
+      <c r="B7" s="24" t="inlineStr">
         <is>
           <t>Формат constraints:
-null_ratio=0..1; 
-is_unique=true/false; 
-allowed_values=[10.5, 20.25]; 
-min_value=0.0; 
-max_value=1000.0; 
-precision=2</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>STRING</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>INT</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>INT</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>INT</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>INT</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="99.75" customHeight="1" s="7">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>DATE</t>
-        </is>
-      </c>
-      <c r="B5" s="10" t="inlineStr">
-        <is>
-          <t>Формат constraints: 
-null_ratio=0..1; 
-is_unique=true/false; 
-allowed_values=["2024-01-01", "2024-01-02"]; 
-min_value="2024-01-01"; 
-max_value="2024-12-31"; 
-date_format="%Y-%m-%d"</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>BOOLEAN</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>TIMESTAMP</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>DATE</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="99.75" customHeight="1" s="7">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>TIMESTAMP</t>
-        </is>
-      </c>
-      <c r="B6" s="10" t="inlineStr">
-        <is>
-          <t>Формат constraints: 
-null_ratio=0..1; 
-is_unique=true/false; 
-allowed_values=["2024-01-01 00:00:00", "2024-01-01 00:01:00"]; 
-min_timestamp="2024-01-01 00:00:00"; 
-max_timestamp="2024-12-31 23:59:59"; 
-timestamp_format="%Y-%m-%d %H:%M:%S"</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="57" customHeight="1" s="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>BOOLEAN</t>
-        </is>
-      </c>
-      <c r="B7" s="10" t="inlineStr">
-        <is>
-          <t>Формат constraints: 
-null_ratio=0..1; 
-is_unique=true/false; 
+null_ratio=0..1;
+is_unique=true/false;
 allowed_values=[true, false]</t>
         </is>
       </c>
@@ -2257,85 +2062,126 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.25"/>
   <cols>
-    <col width="18" customWidth="1" style="7" min="1" max="2"/>
-    <col width="12" customWidth="1" style="7" min="3" max="3"/>
+    <col width="24" customWidth="1" style="7" min="1" max="2"/>
+    <col width="14" customWidth="1" style="7" min="2" max="2"/>
+    <col width="42" customWidth="1" style="7" min="3" max="3"/>
+    <col width="42" customWidth="1" style="7" min="4" max="4"/>
+    <col width="24" customWidth="1" style="7" min="5" max="5"/>
+    <col width="24" customWidth="1" style="7" min="6" max="6"/>
+    <col width="24" customWidth="1" style="7" min="7" max="7"/>
+    <col width="26" customWidth="1" style="7" min="8" max="8"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>source_type</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>source_name</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
+    <row r="1" ht="26" customHeight="1" s="7">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>table_name</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>total_rows</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>hive_target_table</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>iceberg_target_table</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>write_mode</t>
+        </is>
+      </c>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>hive_partition_columns</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>iceberg_partition_columns</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="22" customHeight="1" s="7">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>json</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>example_source</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="24" customHeight="1" s="7">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>schema_name</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>table_name</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>total_rows</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>analytics_db</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
           <t>company_groups</t>
         </is>
       </c>
-      <c r="C7" s="2" t="n">
+      <c r="B2" s="2" t="n">
         <v>5000</v>
       </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>analytics_db</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>hive_db.analytics_db__company_groups</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>iceberg_db.analytics_db__company_groups</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>OVERWRITE_PARTITIONS</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>DATE_PART</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>VALUE_DAY</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="22" customHeight="1" s="7">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>subjects</t>
         </is>
       </c>
-      <c r="C8" s="2" t="n">
+      <c r="B3" s="2" t="n">
         <v>10000</v>
       </c>
-    </row>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>hive_db.analytics_db__subjects</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>iceberg_db.analytics_db__subjects</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>APPEND</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+    </row>
+    <row r="6" ht="24" customHeight="1" s="7"/>
   </sheetData>
+  <autoFilter ref="A1:G200"/>
+  <dataValidations count="1">
+    <dataValidation sqref="E2:E200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+      <formula1>"OVERWRITE_TABLE,OVERWRITE_PARTITIONS,APPEND"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2346,207 +2192,76 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H5"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.25"/>
+  <dimension ref="A1:D2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14.59765625" customWidth="1" style="7" min="1" max="1"/>
-    <col width="14.73046875" customWidth="1" style="7" min="2" max="2"/>
-    <col width="17.33203125" customWidth="1" style="7" min="3" max="3"/>
-    <col width="14.9296875" customWidth="1" style="7" min="4" max="4"/>
-    <col width="20.46484375" customWidth="1" style="7" min="5" max="5"/>
-    <col width="20.59765625" customWidth="1" style="7" min="6" max="6"/>
-    <col width="38.06640625" customWidth="1" style="7" min="7" max="7"/>
-    <col width="39.6640625" customWidth="1" style="7" min="8" max="8"/>
+    <col width="80" customWidth="1" style="7" min="1" max="1"/>
+    <col width="80" customWidth="1" style="7" min="2" max="2"/>
+    <col width="30" customWidth="1" style="7" min="3" max="3"/>
+    <col width="30" customWidth="1" style="7" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1" s="7">
-      <c r="A1" s="15" t="inlineStr">
-        <is>
-          <t>column_name</t>
-        </is>
-      </c>
-      <c r="B1" s="16" t="inlineStr">
-        <is>
-          <t>gen_data_type</t>
-        </is>
-      </c>
-      <c r="C1" s="16" t="inlineStr">
-        <is>
-          <t>output_data_type</t>
-        </is>
-      </c>
-      <c r="D1" s="16" t="inlineStr">
-        <is>
-          <t>is_primary_key</t>
-        </is>
-      </c>
-      <c r="E1" s="16" t="inlineStr">
-        <is>
-          <t>constraints</t>
-        </is>
-      </c>
-      <c r="F1" s="16" t="inlineStr">
-        <is>
-          <t>foreign_key</t>
-        </is>
-      </c>
-      <c r="G1" s="17" t="inlineStr">
-        <is>
-          <t>Подсказка по constraints</t>
-        </is>
-      </c>
-      <c r="H1" s="18" t="inlineStr">
-        <is>
-          <t>Пример заполнения foreign_key</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="114" customHeight="1" s="7">
-      <c r="A2" s="13" t="inlineStr">
-        <is>
-          <t>INN</t>
-        </is>
-      </c>
-      <c r="B2" s="8" t="inlineStr">
-        <is>
-          <t>INT</t>
-        </is>
-      </c>
-      <c r="C2" s="8" t="inlineStr">
-        <is>
-          <t>INT</t>
-        </is>
-      </c>
-      <c r="D2" s="8" t="b">
-        <v>1</v>
-      </c>
-      <c r="E2" s="8" t="inlineStr">
-        <is>
-          <t>digits_count=10</t>
-        </is>
-      </c>
-      <c r="F2" s="8" t="n"/>
-      <c r="G2" s="9">
-        <f>IF($F2&lt;&gt;"","Для foreign_key допустим только null_ratio=0..1. Остальные generator constraints запрещены.",IFERROR(VLOOKUP($B2,'Constant List'!$A$2:$B$7,2,FALSE),"Тип данных не заполнен"))</f>
-        <v/>
-      </c>
-      <c r="H2" s="14">
-        <f>'Constant List'!$J$2</f>
-        <v/>
-      </c>
-    </row>
-    <row r="3" ht="85.5" customHeight="1" s="7">
-      <c r="A3" s="13" t="inlineStr">
-        <is>
-          <t>GROUP_ID_DM</t>
-        </is>
-      </c>
-      <c r="B3" s="8" t="inlineStr">
-        <is>
-          <t>INT</t>
-        </is>
-      </c>
-      <c r="C3" s="8" t="inlineStr">
-        <is>
-          <t>INT</t>
-        </is>
-      </c>
-      <c r="D3" s="8" t="n"/>
-      <c r="E3" s="8" t="inlineStr">
-        <is>
-          <t>null_ratio=0; min_value=1; max_value=6000000</t>
-        </is>
-      </c>
-      <c r="F3" s="8" t="n"/>
-      <c r="G3" s="9">
-        <f>IF($F3&lt;&gt;"","Для foreign_key допустим только null_ratio=0..1. Остальные generator constraints запрещены.",IFERROR(VLOOKUP($B3,'Constant List'!$A$2:$B$7,2,FALSE),"Тип данных не заполнен"))</f>
-        <v/>
-      </c>
-      <c r="H3" s="14">
-        <f>'Constant List'!$J$2</f>
-        <v/>
-      </c>
-    </row>
-    <row r="4" ht="85.5" customHeight="1" s="7">
-      <c r="A4" s="13" t="inlineStr">
-        <is>
-          <t>MAIN_COMPANY_FLG_DM</t>
-        </is>
-      </c>
-      <c r="B4" s="8" t="inlineStr">
-        <is>
-          <t>INT</t>
-        </is>
-      </c>
-      <c r="C4" s="8" t="inlineStr">
-        <is>
-          <t>INT</t>
-        </is>
-      </c>
-      <c r="D4" s="8" t="n"/>
-      <c r="E4" s="8" t="inlineStr">
-        <is>
-          <t>allowed_values=[0, 1]</t>
-        </is>
-      </c>
-      <c r="F4" s="8" t="n"/>
-      <c r="G4" s="9">
-        <f>IF($F4&lt;&gt;"","Для foreign_key допустим только null_ratio=0..1. Остальные generator constraints запрещены.",IFERROR(VLOOKUP($B4,'Constant List'!$A$2:$B$7,2,FALSE),"Тип данных не заполнен"))</f>
-        <v/>
-      </c>
-      <c r="H4" s="14">
-        <f>'Constant List'!$J$2</f>
-        <v/>
-      </c>
-    </row>
-    <row r="5" ht="99.75" customHeight="1" s="7">
-      <c r="A5" s="19" t="inlineStr">
-        <is>
-          <t>VALUE_DAY</t>
-        </is>
-      </c>
-      <c r="B5" s="20" t="inlineStr">
-        <is>
-          <t>DATE</t>
-        </is>
-      </c>
-      <c r="C5" s="20" t="inlineStr">
-        <is>
-          <t>INT</t>
-        </is>
-      </c>
-      <c r="D5" s="20" t="n"/>
-      <c r="E5" s="20" t="inlineStr">
-        <is>
-          <t>date_format="%Y%m%d"</t>
-        </is>
-      </c>
-      <c r="F5" s="20" t="n"/>
-      <c r="G5" s="21">
-        <f>IF($F5&lt;&gt;"","Для foreign_key допустим только null_ratio=0..1. Остальные generator constraints запрещены.",IFERROR(VLOOKUP($B5,'Constant List'!$A$2:$B$7,2,FALSE),"Тип данных не заполнен"))</f>
-        <v/>
-      </c>
-      <c r="H5" s="22">
-        <f>'Constant List'!$J$2</f>
-        <v/>
+    <row r="1" ht="26" customHeight="1" s="7">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>hive_sql</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>iceberg_sql</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>hive_exclude_columns</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>iceberg_exclude_columns</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="44" customHeight="1" s="7">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>SELECT
+    cg.GROUP_ID_DM,
+    cg.MAIN_COMPANY_FLG_DM,
+    COUNT(s.IDSUBJECT) AS subject_count,
+    COUNT(s.SOGRN) AS with_ogrn_count
+FROM hive_db.analytics_db__company_groups cg
+JOIN hive_db.analytics_db__subjects s ON cg.INN = s.SINN
+GROUP BY cg.GROUP_ID_DM, cg.MAIN_COMPANY_FLG_DM</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>SELECT
+    cg.GROUP_ID_DM,
+    cg.MAIN_COMPANY_FLG_DM,
+    COUNT(s.IDSUBJECT) AS subject_count,
+    COUNT(s.SOGRN) AS with_ogrn_count
+FROM iceberg_db.analytics_db__company_groups cg
+JOIN iceberg_db.analytics_db__subjects s ON cg.INN = s.SINN
+GROUP BY cg.GROUP_ID_DM, cg.MAIN_COMPANY_FLG_DM</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>date_part, year_part, month_part</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>date_part, year_part, month_part</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="3">
-    <dataValidation sqref="B2:B5" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>GEN_TYPES</formula1>
-    </dataValidation>
-    <dataValidation sqref="D2:D5" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>BOOL_VALUES</formula1>
-    </dataValidation>
-    <dataValidation sqref="C2:C5" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>IF($B2="",GEN_TYPES,INDIRECT("OUTPUT_TYPES_"&amp;$B2))</formula1>
-    </dataValidation>
-  </dataValidations>
+  <autoFilter ref="A1:D20"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-  </tableParts>
 </worksheet>
 </file>
 
@@ -2556,17 +2271,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H8"/>
+  <dimension ref="A1:K6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.25"/>
   <cols>
-    <col width="14.19921875" customWidth="1" style="7" min="1" max="1"/>
-    <col width="14.73046875" customWidth="1" style="7" min="2" max="2"/>
-    <col width="17.33203125" customWidth="1" style="7" min="3" max="3"/>
-    <col width="14.9296875" customWidth="1" style="7" min="4" max="4"/>
-    <col width="21" customWidth="1" style="7" min="5" max="5"/>
-    <col width="26.33203125" customWidth="1" style="7" min="6" max="6"/>
-    <col width="57.59765625" customWidth="1" style="7" min="7" max="7"/>
-    <col width="38.6640625" bestFit="1" customWidth="1" style="7" min="8" max="8"/>
+    <col width="20" customWidth="1" style="7" min="1" max="1"/>
+    <col width="16" customWidth="1" style="7" min="2" max="2"/>
+    <col width="18" customWidth="1" style="7" min="3" max="3"/>
+    <col width="14" customWidth="1" style="7" min="4" max="4"/>
+    <col width="48" customWidth="1" style="7" min="5" max="5"/>
+    <col width="38" customWidth="1" style="7" min="6" max="6"/>
+    <col width="16" customWidth="1" style="7" min="7" max="7"/>
+    <col width="36" customWidth="1" style="7" min="8" max="8"/>
+    <col width="58" customWidth="1" style="7" min="9" max="9"/>
+    <col width="34" customWidth="1" style="7" min="10" max="10"/>
+    <col width="34" customWidth="1" style="7" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1" s="7">
@@ -2575,281 +2293,660 @@
           <t>column_name</t>
         </is>
       </c>
-      <c r="B1" s="16" t="inlineStr">
+      <c r="B1" s="15" t="inlineStr">
         <is>
           <t>gen_data_type</t>
         </is>
       </c>
-      <c r="C1" s="16" t="inlineStr">
+      <c r="C1" s="15" t="inlineStr">
         <is>
           <t>output_data_type</t>
         </is>
       </c>
-      <c r="D1" s="16" t="inlineStr">
+      <c r="D1" s="15" t="inlineStr">
         <is>
           <t>is_primary_key</t>
         </is>
       </c>
-      <c r="E1" s="16" t="inlineStr">
+      <c r="E1" s="15" t="inlineStr">
         <is>
           <t>constraints</t>
         </is>
       </c>
-      <c r="F1" s="16" t="inlineStr">
+      <c r="F1" s="15" t="inlineStr">
         <is>
           <t>foreign_key</t>
         </is>
       </c>
-      <c r="G1" s="17" t="inlineStr">
-        <is>
-          <t>Подсказка по constraints</t>
-        </is>
-      </c>
-      <c r="H1" s="18" t="inlineStr">
+      <c r="G1" s="15" t="inlineStr">
+        <is>
+          <t>engine_scope</t>
+        </is>
+      </c>
+      <c r="H1" s="15" t="inlineStr">
+        <is>
+          <t>derive</t>
+        </is>
+      </c>
+      <c r="I1" s="17" t="inlineStr">
+        <is>
+          <t>Подсказка</t>
+        </is>
+      </c>
+      <c r="J1" s="17" t="inlineStr">
         <is>
           <t>Пример заполнения foreign_key</t>
         </is>
       </c>
-    </row>
-    <row r="2" ht="128.25" customHeight="1" s="7">
+      <c r="K1" s="18" t="inlineStr">
+        <is>
+          <t>Пример заполнения derive</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="28" customHeight="1" s="7">
       <c r="A2" s="13" t="inlineStr">
         <is>
-          <t>STYPE</t>
-        </is>
-      </c>
-      <c r="B2" s="8" t="inlineStr">
-        <is>
-          <t>STRING</t>
-        </is>
-      </c>
-      <c r="C2" s="8" t="inlineStr">
-        <is>
-          <t>STRING</t>
-        </is>
-      </c>
-      <c r="D2" s="8" t="n"/>
-      <c r="E2" s="8" t="inlineStr">
-        <is>
-          <t>allowed_values=["c", "cpr"]</t>
-        </is>
-      </c>
-      <c r="F2" s="8" t="n"/>
-      <c r="G2" s="9">
-        <f>IF($F2&lt;&gt;"","Для foreign_key допустим только null_ratio=0..1. Остальные generator constraints запрещены.",IFERROR(VLOOKUP($B2,'Constant List'!$A$2:$B$7,2,FALSE),"Тип данных не заполнен"))</f>
-        <v/>
-      </c>
-      <c r="H2" s="14">
+          <t>INN</t>
+        </is>
+      </c>
+      <c r="B2" s="13" t="inlineStr">
+        <is>
+          <t>INT</t>
+        </is>
+      </c>
+      <c r="C2" s="13" t="inlineStr">
+        <is>
+          <t>INT</t>
+        </is>
+      </c>
+      <c r="D2" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="E2" s="13" t="inlineStr">
+        <is>
+          <t>digits_count=10</t>
+        </is>
+      </c>
+      <c r="F2" s="13" t="n"/>
+      <c r="G2" s="13" t="inlineStr">
+        <is>
+          <t>both</t>
+        </is>
+      </c>
+      <c r="H2" s="13" t="n"/>
+      <c r="I2" s="9">
+        <f>IF($F2&lt;&gt;"","Для foreign_key допустим только null_ratio=0..1. gen_data_type и output_data_type выводятся из parent column.",IF($H2&lt;&gt;"","Для derive укажите output_data_type и engine_scope; gen_data_type/constraints/foreign_key оставьте пустыми.",IFERROR(VLOOKUP($B2,'Constant List'!$A$2:$B$7,2,FALSE),"Тип генерации не заполнен")))</f>
+        <v/>
+      </c>
+      <c r="J2" s="9">
         <f>'Constant List'!$J$2</f>
         <v/>
       </c>
-    </row>
-    <row r="3" ht="57" customHeight="1" s="7">
+      <c r="K2" s="14">
+        <f>'Constant List'!$K$2</f>
+        <v/>
+      </c>
+    </row>
+    <row r="3" ht="46" customHeight="1" s="7">
       <c r="A3" s="13" t="inlineStr">
         <is>
-          <t>SINN</t>
-        </is>
-      </c>
-      <c r="B3" s="8" t="inlineStr">
+          <t>GROUP_ID_DM</t>
+        </is>
+      </c>
+      <c r="B3" s="13" t="inlineStr">
         <is>
           <t>INT</t>
         </is>
       </c>
-      <c r="C3" s="8" t="inlineStr">
+      <c r="C3" s="13" t="inlineStr">
         <is>
           <t>INT</t>
         </is>
       </c>
-      <c r="D3" s="8" t="n"/>
-      <c r="E3" s="8" t="n"/>
-      <c r="F3" s="8" t="inlineStr">
-        <is>
-          <t>schema_name="analytics_db"; table_name="company_groups"; column_name="INN"; relation_type="ONE_TO_MANY"</t>
-        </is>
-      </c>
-      <c r="G3" s="9">
-        <f>IF($F3&lt;&gt;"","Для foreign_key допустим только null_ratio=0..1. Остальные generator constraints запрещены.",IFERROR(VLOOKUP($B3,'Constant List'!$A$2:$B$7,2,FALSE),"Тип данных не заполнен"))</f>
-        <v/>
-      </c>
-      <c r="H3" s="14">
+      <c r="D3" s="13" t="n"/>
+      <c r="E3" s="13" t="inlineStr">
+        <is>
+          <t>null_ratio=0; min_value=1; max_value=6000000</t>
+        </is>
+      </c>
+      <c r="F3" s="13" t="n"/>
+      <c r="G3" s="13" t="inlineStr">
+        <is>
+          <t>both</t>
+        </is>
+      </c>
+      <c r="H3" s="13" t="n"/>
+      <c r="I3" s="9">
+        <f>IF($F3&lt;&gt;"","Для foreign_key допустим только null_ratio=0..1. gen_data_type и output_data_type выводятся из parent column.",IF($H3&lt;&gt;"","Для derive укажите output_data_type и engine_scope; gen_data_type/constraints/foreign_key оставьте пустыми.",IFERROR(VLOOKUP($B3,'Constant List'!$A$2:$B$7,2,FALSE),"Тип генерации не заполнен")))</f>
+        <v/>
+      </c>
+      <c r="J3" s="9">
         <f>'Constant List'!$J$2</f>
         <v/>
       </c>
-    </row>
-    <row r="4" ht="85.5" customHeight="1" s="7">
+      <c r="K3" s="14">
+        <f>'Constant List'!$K$2</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4" ht="28" customHeight="1" s="7">
       <c r="A4" s="13" t="inlineStr">
         <is>
-          <t>SOGRN</t>
-        </is>
-      </c>
-      <c r="B4" s="8" t="inlineStr">
+          <t>MAIN_COMPANY_FLG_DM</t>
+        </is>
+      </c>
+      <c r="B4" s="13" t="inlineStr">
         <is>
           <t>INT</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="13" t="inlineStr">
         <is>
           <t>INT</t>
         </is>
       </c>
-      <c r="D4" s="8" t="n"/>
-      <c r="E4" s="8" t="inlineStr">
-        <is>
-          <t>null_ratio=0.1; min_value=1000000000000; max_value=999999999999999</t>
-        </is>
-      </c>
-      <c r="F4" s="8" t="n"/>
-      <c r="G4" s="9">
-        <f>IF($F4&lt;&gt;"","Для foreign_key допустим только null_ratio=0..1. Остальные generator constraints запрещены.",IFERROR(VLOOKUP($B4,'Constant List'!$A$2:$B$7,2,FALSE),"Тип данных не заполнен"))</f>
-        <v/>
-      </c>
-      <c r="H4" s="14">
+      <c r="D4" s="13" t="n"/>
+      <c r="E4" s="13" t="inlineStr">
+        <is>
+          <t>allowed_values=[0, 1]</t>
+        </is>
+      </c>
+      <c r="F4" s="13" t="n"/>
+      <c r="G4" s="13" t="inlineStr">
+        <is>
+          <t>both</t>
+        </is>
+      </c>
+      <c r="H4" s="13" t="n"/>
+      <c r="I4" s="9">
+        <f>IF($F4&lt;&gt;"","Для foreign_key допустим только null_ratio=0..1. gen_data_type и output_data_type выводятся из parent column.",IF($H4&lt;&gt;"","Для derive укажите output_data_type и engine_scope; gen_data_type/constraints/foreign_key оставьте пустыми.",IFERROR(VLOOKUP($B4,'Constant List'!$A$2:$B$7,2,FALSE),"Тип генерации не заполнен")))</f>
+        <v/>
+      </c>
+      <c r="J4" s="9">
         <f>'Constant List'!$J$2</f>
         <v/>
       </c>
-    </row>
-    <row r="5" ht="128.25" customHeight="1" s="7">
+      <c r="K4" s="14">
+        <f>'Constant List'!$K$2</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5" ht="46" customHeight="1" s="7">
       <c r="A5" s="13" t="inlineStr">
         <is>
-          <t>SPIN</t>
-        </is>
-      </c>
-      <c r="B5" s="8" t="inlineStr">
-        <is>
-          <t>STRING</t>
-        </is>
-      </c>
-      <c r="C5" s="8" t="inlineStr">
-        <is>
-          <t>STRING</t>
-        </is>
-      </c>
-      <c r="D5" s="8" t="n"/>
-      <c r="E5" s="8" t="inlineStr">
-        <is>
-          <t>null_ratio=0.1; length=6; case_mode="upper"; regular_expr="^[A-Z0-9]{6}$"</t>
-        </is>
-      </c>
-      <c r="F5" s="8" t="n"/>
-      <c r="G5" s="9">
-        <f>IF($F5&lt;&gt;"","Для foreign_key допустим только null_ratio=0..1. Остальные generator constraints запрещены.",IFERROR(VLOOKUP($B5,'Constant List'!$A$2:$B$7,2,FALSE),"Тип данных не заполнен"))</f>
-        <v/>
-      </c>
-      <c r="H5" s="14">
+          <t>VALUE_DAY</t>
+        </is>
+      </c>
+      <c r="B5" s="13" t="inlineStr">
+        <is>
+          <t>DATE</t>
+        </is>
+      </c>
+      <c r="C5" s="13" t="inlineStr">
+        <is>
+          <t>DATE</t>
+        </is>
+      </c>
+      <c r="D5" s="13" t="n"/>
+      <c r="E5" s="13" t="inlineStr">
+        <is>
+          <t>min_value="2025-01-01"; max_value="2025-12-31"</t>
+        </is>
+      </c>
+      <c r="F5" s="13" t="n"/>
+      <c r="G5" s="13" t="inlineStr">
+        <is>
+          <t>both</t>
+        </is>
+      </c>
+      <c r="H5" s="13" t="n"/>
+      <c r="I5" s="9">
+        <f>IF($F5&lt;&gt;"","Для foreign_key допустим только null_ratio=0..1. gen_data_type и output_data_type выводятся из parent column.",IF($H5&lt;&gt;"","Для derive укажите output_data_type и engine_scope; gen_data_type/constraints/foreign_key оставьте пустыми.",IFERROR(VLOOKUP($B5,'Constant List'!$A$2:$B$7,2,FALSE),"Тип генерации не заполнен")))</f>
+        <v/>
+      </c>
+      <c r="J5" s="9">
         <f>'Constant List'!$J$2</f>
         <v/>
       </c>
-    </row>
-    <row r="6" ht="128.25" customHeight="1" s="7">
+      <c r="K5" s="14">
+        <f>'Constant List'!$K$2</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6" ht="28" customHeight="1" s="7">
       <c r="A6" s="13" t="inlineStr">
         <is>
-          <t>SABSCODE</t>
-        </is>
-      </c>
-      <c r="B6" s="8" t="inlineStr">
-        <is>
-          <t>STRING</t>
-        </is>
-      </c>
-      <c r="C6" s="8" t="inlineStr">
-        <is>
-          <t>STRING</t>
-        </is>
-      </c>
-      <c r="D6" s="8" t="n"/>
-      <c r="E6" s="8" t="inlineStr">
-        <is>
-          <t>allowed_values=["SFAProd"]</t>
-        </is>
-      </c>
-      <c r="F6" s="8" t="n"/>
-      <c r="G6" s="9">
-        <f>IF($F6&lt;&gt;"","Для foreign_key допустим только null_ratio=0..1. Остальные generator constraints запрещены.",IFERROR(VLOOKUP($B6,'Constant List'!$A$2:$B$7,2,FALSE),"Тип данных не заполнен"))</f>
-        <v/>
-      </c>
-      <c r="H6" s="14">
+          <t>DATE_PART</t>
+        </is>
+      </c>
+      <c r="B6" s="13" t="n"/>
+      <c r="C6" s="13" t="inlineStr">
+        <is>
+          <t>INT</t>
+        </is>
+      </c>
+      <c r="D6" s="13" t="n"/>
+      <c r="E6" s="13" t="n"/>
+      <c r="F6" s="13" t="n"/>
+      <c r="G6" s="13" t="inlineStr">
+        <is>
+          <t>hive_only</t>
+        </is>
+      </c>
+      <c r="H6" s="13" t="inlineStr">
+        <is>
+          <t>source_column="VALUE_DAY"; rule="YYYYMMDD"</t>
+        </is>
+      </c>
+      <c r="I6" s="9">
+        <f>IF($F6&lt;&gt;"","Для foreign_key допустим только null_ratio=0..1. gen_data_type и output_data_type выводятся из parent column.",IF($H6&lt;&gt;"","Для derive укажите output_data_type и engine_scope; gen_data_type/constraints/foreign_key оставьте пустыми.",IFERROR(VLOOKUP($B6,'Constant List'!$A$2:$B$7,2,FALSE),"Тип генерации не заполнен")))</f>
+        <v/>
+      </c>
+      <c r="J6" s="9">
         <f>'Constant List'!$J$2</f>
         <v/>
       </c>
-    </row>
-    <row r="7" ht="128.25" customHeight="1" s="7">
-      <c r="A7" s="13" t="inlineStr">
-        <is>
-          <t>SPINSFA</t>
-        </is>
-      </c>
-      <c r="B7" s="8" t="inlineStr">
-        <is>
-          <t>STRING</t>
-        </is>
-      </c>
-      <c r="C7" s="8" t="inlineStr">
-        <is>
-          <t>STRING</t>
-        </is>
-      </c>
-      <c r="D7" s="8" t="n"/>
-      <c r="E7" s="8" t="inlineStr">
-        <is>
-          <t>regular_expr="^ABR-FW-SCRMFW-WORK-ACCOUNT ACB-[0-9]{1,20}$"</t>
-        </is>
-      </c>
-      <c r="F7" s="8" t="n"/>
-      <c r="G7" s="9">
-        <f>IF($F7&lt;&gt;"","Для foreign_key допустим только null_ratio=0..1. Остальные generator constraints запрещены.",IFERROR(VLOOKUP($B7,'Constant List'!$A$2:$B$7,2,FALSE),"Тип данных не заполнен"))</f>
-        <v/>
-      </c>
-      <c r="H7" s="14">
-        <f>'Constant List'!$J$2</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8" ht="85.5" customHeight="1" s="7">
-      <c r="A8" s="19" t="inlineStr">
-        <is>
-          <t>IDSUBJECT</t>
-        </is>
-      </c>
-      <c r="B8" s="20" t="inlineStr">
-        <is>
-          <t>INT</t>
-        </is>
-      </c>
-      <c r="C8" s="20" t="inlineStr">
-        <is>
-          <t>INT</t>
-        </is>
-      </c>
-      <c r="D8" s="20" t="n"/>
-      <c r="E8" s="20" t="inlineStr">
-        <is>
-          <t>min_value=1; max_value=20000000</t>
-        </is>
-      </c>
-      <c r="F8" s="20" t="n"/>
-      <c r="G8" s="21">
-        <f>IF($F8&lt;&gt;"","Для foreign_key допустим только null_ratio=0..1. Остальные generator constraints запрещены.",IFERROR(VLOOKUP($B8,'Constant List'!$A$2:$B$7,2,FALSE),"Тип данных не заполнен"))</f>
-        <v/>
-      </c>
-      <c r="H8" s="22">
-        <f>'Constant List'!$J$2</f>
+      <c r="K6" s="14">
+        <f>'Constant List'!$K$2</f>
         <v/>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:K6"/>
   <dataValidations count="3">
-    <dataValidation sqref="B2:B8" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>GEN_TYPES</formula1>
+    <dataValidation sqref="B2:B500 C2:C500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"STRING,INT,FLOAT,DATE,TIMESTAMP,BOOLEAN"</formula1>
     </dataValidation>
-    <dataValidation sqref="D2:D8" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>BOOL_VALUES</formula1>
+    <dataValidation sqref="G2:G500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"both,hive_only,iceberg_only"</formula1>
     </dataValidation>
-    <dataValidation sqref="C2:C8" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>IF($B2="",GEN_TYPES,INDIRECT("OUTPUT_TYPES_"&amp;$B2))</formula1>
+    <dataValidation sqref="D2:D500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"TRUE,FALSE"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.25"/>
+  <cols>
+    <col width="20" customWidth="1" style="7" min="1" max="1"/>
+    <col width="16" customWidth="1" style="7" min="2" max="2"/>
+    <col width="18" customWidth="1" style="7" min="3" max="3"/>
+    <col width="14" customWidth="1" style="7" min="4" max="4"/>
+    <col width="48" customWidth="1" style="7" min="5" max="5"/>
+    <col width="38" customWidth="1" style="7" min="6" max="6"/>
+    <col width="16" customWidth="1" style="7" min="7" max="7"/>
+    <col width="36" bestFit="1" customWidth="1" style="7" min="8" max="8"/>
+    <col width="58" customWidth="1" style="7" min="9" max="9"/>
+    <col width="34" customWidth="1" style="7" min="10" max="10"/>
+    <col width="34" customWidth="1" style="7" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1" s="7">
+      <c r="A1" s="15" t="inlineStr">
+        <is>
+          <t>column_name</t>
+        </is>
+      </c>
+      <c r="B1" s="15" t="inlineStr">
+        <is>
+          <t>gen_data_type</t>
+        </is>
+      </c>
+      <c r="C1" s="15" t="inlineStr">
+        <is>
+          <t>output_data_type</t>
+        </is>
+      </c>
+      <c r="D1" s="15" t="inlineStr">
+        <is>
+          <t>is_primary_key</t>
+        </is>
+      </c>
+      <c r="E1" s="15" t="inlineStr">
+        <is>
+          <t>constraints</t>
+        </is>
+      </c>
+      <c r="F1" s="15" t="inlineStr">
+        <is>
+          <t>foreign_key</t>
+        </is>
+      </c>
+      <c r="G1" s="15" t="inlineStr">
+        <is>
+          <t>engine_scope</t>
+        </is>
+      </c>
+      <c r="H1" s="15" t="inlineStr">
+        <is>
+          <t>derive</t>
+        </is>
+      </c>
+      <c r="I1" s="17" t="inlineStr">
+        <is>
+          <t>Подсказка</t>
+        </is>
+      </c>
+      <c r="J1" s="17" t="inlineStr">
+        <is>
+          <t>Пример заполнения foreign_key</t>
+        </is>
+      </c>
+      <c r="K1" s="18" t="inlineStr">
+        <is>
+          <t>Пример заполнения derive</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="28" customHeight="1" s="7">
+      <c r="A2" s="13" t="inlineStr">
+        <is>
+          <t>STYPE</t>
+        </is>
+      </c>
+      <c r="B2" s="13" t="inlineStr">
+        <is>
+          <t>STRING</t>
+        </is>
+      </c>
+      <c r="C2" s="13" t="inlineStr">
+        <is>
+          <t>STRING</t>
+        </is>
+      </c>
+      <c r="D2" s="13" t="n"/>
+      <c r="E2" s="13" t="inlineStr">
+        <is>
+          <t>allowed_values=["c", "cpr"]</t>
+        </is>
+      </c>
+      <c r="F2" s="13" t="n"/>
+      <c r="G2" s="13" t="inlineStr">
+        <is>
+          <t>both</t>
+        </is>
+      </c>
+      <c r="H2" s="13" t="n"/>
+      <c r="I2" s="9">
+        <f>IF($F2&lt;&gt;"","Для foreign_key допустим только null_ratio=0..1. gen_data_type и output_data_type выводятся из parent column.",IF($H2&lt;&gt;"","Для derive укажите output_data_type и engine_scope; gen_data_type/constraints/foreign_key оставьте пустыми.",IFERROR(VLOOKUP($B2,'Constant List'!$A$2:$B$7,2,FALSE),"Тип генерации не заполнен")))</f>
+        <v/>
+      </c>
+      <c r="J2" s="9">
+        <f>'Constant List'!$J$2</f>
+        <v/>
+      </c>
+      <c r="K2" s="14">
+        <f>'Constant List'!$K$2</f>
+        <v/>
+      </c>
+    </row>
+    <row r="3" ht="46" customHeight="1" s="7">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>SINN</t>
+        </is>
+      </c>
+      <c r="B3" s="13" t="n"/>
+      <c r="C3" s="13" t="n"/>
+      <c r="D3" s="13" t="n"/>
+      <c r="E3" s="13" t="n"/>
+      <c r="F3" s="13" t="inlineStr">
+        <is>
+          <t>table_name="company_groups"; column_name="INN"; relation_type="ONE_TO_MANY"</t>
+        </is>
+      </c>
+      <c r="G3" s="13" t="inlineStr">
+        <is>
+          <t>both</t>
+        </is>
+      </c>
+      <c r="H3" s="13" t="n"/>
+      <c r="I3" s="9">
+        <f>IF($F3&lt;&gt;"","Для foreign_key допустим только null_ratio=0..1. gen_data_type и output_data_type выводятся из parent column.",IF($H3&lt;&gt;"","Для derive укажите output_data_type и engine_scope; gen_data_type/constraints/foreign_key оставьте пустыми.",IFERROR(VLOOKUP($B3,'Constant List'!$A$2:$B$7,2,FALSE),"Тип генерации не заполнен")))</f>
+        <v/>
+      </c>
+      <c r="J3" s="9">
+        <f>'Constant List'!$J$2</f>
+        <v/>
+      </c>
+      <c r="K3" s="14">
+        <f>'Constant List'!$K$2</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4" ht="46" customHeight="1" s="7">
+      <c r="A4" s="13" t="inlineStr">
+        <is>
+          <t>SOGRN</t>
+        </is>
+      </c>
+      <c r="B4" s="13" t="inlineStr">
+        <is>
+          <t>INT</t>
+        </is>
+      </c>
+      <c r="C4" s="13" t="inlineStr">
+        <is>
+          <t>INT</t>
+        </is>
+      </c>
+      <c r="D4" s="13" t="n"/>
+      <c r="E4" s="13" t="inlineStr">
+        <is>
+          <t>null_ratio=0.1; min_value=1000000000000; max_value=999999999999999</t>
+        </is>
+      </c>
+      <c r="F4" s="13" t="n"/>
+      <c r="G4" s="13" t="inlineStr">
+        <is>
+          <t>both</t>
+        </is>
+      </c>
+      <c r="H4" s="13" t="n"/>
+      <c r="I4" s="9">
+        <f>IF($F4&lt;&gt;"","Для foreign_key допустим только null_ratio=0..1. gen_data_type и output_data_type выводятся из parent column.",IF($H4&lt;&gt;"","Для derive укажите output_data_type и engine_scope; gen_data_type/constraints/foreign_key оставьте пустыми.",IFERROR(VLOOKUP($B4,'Constant List'!$A$2:$B$7,2,FALSE),"Тип генерации не заполнен")))</f>
+        <v/>
+      </c>
+      <c r="J4" s="9">
+        <f>'Constant List'!$J$2</f>
+        <v/>
+      </c>
+      <c r="K4" s="14">
+        <f>'Constant List'!$K$2</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5" ht="46" customHeight="1" s="7">
+      <c r="A5" s="13" t="inlineStr">
+        <is>
+          <t>SPIN</t>
+        </is>
+      </c>
+      <c r="B5" s="13" t="inlineStr">
+        <is>
+          <t>STRING</t>
+        </is>
+      </c>
+      <c r="C5" s="13" t="inlineStr">
+        <is>
+          <t>STRING</t>
+        </is>
+      </c>
+      <c r="D5" s="13" t="n"/>
+      <c r="E5" s="13" t="inlineStr">
+        <is>
+          <t>null_ratio=0.1; length=6; case_mode="upper"; regular_expr="^[A-Z0-9]{6}$"</t>
+        </is>
+      </c>
+      <c r="F5" s="13" t="n"/>
+      <c r="G5" s="13" t="inlineStr">
+        <is>
+          <t>both</t>
+        </is>
+      </c>
+      <c r="H5" s="13" t="n"/>
+      <c r="I5" s="9">
+        <f>IF($F5&lt;&gt;"","Для foreign_key допустим только null_ratio=0..1. gen_data_type и output_data_type выводятся из parent column.",IF($H5&lt;&gt;"","Для derive укажите output_data_type и engine_scope; gen_data_type/constraints/foreign_key оставьте пустыми.",IFERROR(VLOOKUP($B5,'Constant List'!$A$2:$B$7,2,FALSE),"Тип генерации не заполнен")))</f>
+        <v/>
+      </c>
+      <c r="J5" s="9">
+        <f>'Constant List'!$J$2</f>
+        <v/>
+      </c>
+      <c r="K5" s="14">
+        <f>'Constant List'!$K$2</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6" ht="28" customHeight="1" s="7">
+      <c r="A6" s="13" t="inlineStr">
+        <is>
+          <t>SABSCODE</t>
+        </is>
+      </c>
+      <c r="B6" s="13" t="inlineStr">
+        <is>
+          <t>STRING</t>
+        </is>
+      </c>
+      <c r="C6" s="13" t="inlineStr">
+        <is>
+          <t>STRING</t>
+        </is>
+      </c>
+      <c r="D6" s="13" t="n"/>
+      <c r="E6" s="13" t="inlineStr">
+        <is>
+          <t>allowed_values=["SFAProd"]</t>
+        </is>
+      </c>
+      <c r="F6" s="13" t="n"/>
+      <c r="G6" s="13" t="inlineStr">
+        <is>
+          <t>both</t>
+        </is>
+      </c>
+      <c r="H6" s="13" t="n"/>
+      <c r="I6" s="9">
+        <f>IF($F6&lt;&gt;"","Для foreign_key допустим только null_ratio=0..1. gen_data_type и output_data_type выводятся из parent column.",IF($H6&lt;&gt;"","Для derive укажите output_data_type и engine_scope; gen_data_type/constraints/foreign_key оставьте пустыми.",IFERROR(VLOOKUP($B6,'Constant List'!$A$2:$B$7,2,FALSE),"Тип генерации не заполнен")))</f>
+        <v/>
+      </c>
+      <c r="J6" s="9">
+        <f>'Constant List'!$J$2</f>
+        <v/>
+      </c>
+      <c r="K6" s="14">
+        <f>'Constant List'!$K$2</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="46" customHeight="1" s="7">
+      <c r="A7" s="13" t="inlineStr">
+        <is>
+          <t>SPINSFA</t>
+        </is>
+      </c>
+      <c r="B7" s="13" t="inlineStr">
+        <is>
+          <t>STRING</t>
+        </is>
+      </c>
+      <c r="C7" s="13" t="inlineStr">
+        <is>
+          <t>STRING</t>
+        </is>
+      </c>
+      <c r="D7" s="13" t="n"/>
+      <c r="E7" s="13" t="inlineStr">
+        <is>
+          <t>regular_expr="^ABR-FW-SCRMFW-WORK-ACCOUNT ACB-[0-9]{1,20}$"</t>
+        </is>
+      </c>
+      <c r="F7" s="13" t="n"/>
+      <c r="G7" s="13" t="inlineStr">
+        <is>
+          <t>both</t>
+        </is>
+      </c>
+      <c r="H7" s="13" t="n"/>
+      <c r="I7" s="9">
+        <f>IF($F7&lt;&gt;"","Для foreign_key допустим только null_ratio=0..1. gen_data_type и output_data_type выводятся из parent column.",IF($H7&lt;&gt;"","Для derive укажите output_data_type и engine_scope; gen_data_type/constraints/foreign_key оставьте пустыми.",IFERROR(VLOOKUP($B7,'Constant List'!$A$2:$B$7,2,FALSE),"Тип генерации не заполнен")))</f>
+        <v/>
+      </c>
+      <c r="J7" s="9">
+        <f>'Constant List'!$J$2</f>
+        <v/>
+      </c>
+      <c r="K7" s="14">
+        <f>'Constant List'!$K$2</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" ht="28" customHeight="1" s="7">
+      <c r="A8" s="13" t="inlineStr">
+        <is>
+          <t>IDSUBJECT</t>
+        </is>
+      </c>
+      <c r="B8" s="13" t="inlineStr">
+        <is>
+          <t>INT</t>
+        </is>
+      </c>
+      <c r="C8" s="13" t="inlineStr">
+        <is>
+          <t>INT</t>
+        </is>
+      </c>
+      <c r="D8" s="13" t="n"/>
+      <c r="E8" s="13" t="inlineStr">
+        <is>
+          <t>min_value=1; max_value=20000000</t>
+        </is>
+      </c>
+      <c r="F8" s="13" t="n"/>
+      <c r="G8" s="13" t="inlineStr">
+        <is>
+          <t>both</t>
+        </is>
+      </c>
+      <c r="H8" s="13" t="n"/>
+      <c r="I8" s="9">
+        <f>IF($F8&lt;&gt;"","Для foreign_key допустим только null_ratio=0..1. gen_data_type и output_data_type выводятся из parent column.",IF($H8&lt;&gt;"","Для derive укажите output_data_type и engine_scope; gen_data_type/constraints/foreign_key оставьте пустыми.",IFERROR(VLOOKUP($B8,'Constant List'!$A$2:$B$7,2,FALSE),"Тип генерации не заполнен")))</f>
+        <v/>
+      </c>
+      <c r="J8" s="9">
+        <f>'Constant List'!$J$2</f>
+        <v/>
+      </c>
+      <c r="K8" s="14">
+        <f>'Constant List'!$K$2</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:K8"/>
+  <dataValidations count="3">
+    <dataValidation sqref="B2:B500 C2:C500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"STRING,INT,FLOAT,DATE,TIMESTAMP,BOOLEAN"</formula1>
+    </dataValidation>
+    <dataValidation sqref="G2:G500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"both,hive_only,iceberg_only"</formula1>
+    </dataValidation>
+    <dataValidation sqref="D2:D500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"TRUE,FALSE"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/datagen/params/data_gen.xlsx
+++ b/datagen/params/data_gen.xlsx
@@ -1343,7 +1343,7 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>На листе tables заполните table_name, total_rows, явные target tables, общий write_mode и partition columns по каждому engine.</t>
+          <t>На листе tables заполните table_name, total_rows, явные target tables и общий write_mode.</t>
         </is>
       </c>
     </row>
@@ -1551,24 +1551,24 @@
     <row r="22" ht="44" customHeight="1" s="7">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>hive_partition_columns</t>
+          <t>partition metadata</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>Опционально. Список partition columns через запятую для Hive. Обязателен только для OVERWRITE_PARTITIONS.</t>
+          <t>Не задаётся в workbook. Loader читает partition columns из реальной target table только для partition-scoped режимов.</t>
         </is>
       </c>
     </row>
     <row r="23" ht="44" customHeight="1" s="7">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>iceberg_partition_columns</t>
+          <t/>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>Опционально. Список partition columns через запятую для Iceberg. Обязателен только для OVERWRITE_PARTITIONS.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -1775,7 +1775,7 @@
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>Для APPEND и OVERWRITE_TABLE могут быть пустыми. Для OVERWRITE_PARTITIONS обязаны быть заполнены отдельно по каждому engine.</t>
+          <t>OVERWRITE_PARTITIONS и APPEND_DISTINCT_PARTITIONS допустимы только для реально partitioned target tables.</t>
         </is>
       </c>
     </row>
@@ -2062,7 +2062,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:E3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.25"/>
   <cols>
     <col width="24" customWidth="1" style="7" min="1" max="2"/>
@@ -2101,16 +2101,6 @@
           <t>write_mode</t>
         </is>
       </c>
-      <c r="F1" s="3" t="inlineStr">
-        <is>
-          <t>hive_partition_columns</t>
-        </is>
-      </c>
-      <c r="G1" s="3" t="inlineStr">
-        <is>
-          <t>iceberg_partition_columns</t>
-        </is>
-      </c>
     </row>
     <row r="2" ht="22" customHeight="1" s="7">
       <c r="A2" s="2" t="inlineStr">
@@ -2136,16 +2126,6 @@
           <t>OVERWRITE_PARTITIONS</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>DATE_PART</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>VALUE_DAY</t>
-        </is>
-      </c>
     </row>
     <row r="3" ht="22" customHeight="1" s="7">
       <c r="A3" s="2" t="inlineStr">
@@ -2171,8 +2151,6 @@
           <t>APPEND</t>
         </is>
       </c>
-      <c r="F3" s="2" t="n"/>
-      <c r="G3" s="2" t="n"/>
     </row>
     <row r="6" ht="24" customHeight="1" s="7"/>
   </sheetData>

--- a/datagen/params/data_gen.xlsx
+++ b/datagen/params/data_gen.xlsx
@@ -1556,7 +1556,7 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>Не задаётся в workbook. Loader читает partition columns из реальной target table только для partition-scoped режимов.</t>
+          <t>Не задаётся в workbook. Partition behavior определяется реальной target table и выбранным write_mode.</t>
         </is>
       </c>
     </row>
@@ -1775,7 +1775,7 @@
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>OVERWRITE_PARTITIONS и APPEND_DISTINCT_PARTITIONS допустимы только для реально partitioned target tables.</t>
+          <t>OVERWRITE_PARTITIONS используйте только для реально partitioned target tables.</t>
         </is>
       </c>
     </row>

--- a/datagen/params/data_gen.xlsx
+++ b/datagen/params/data_gen.xlsx
@@ -107,7 +107,7 @@
     <t>Шаг 11</t>
   </si>
   <si>
-    <t>engine_scope: both по умолчанию. hive_only и iceberg_only используйте только для колонок, которые реально нужны одному движку.</t>
+    <t>engine_scope: ALL по умолчанию. HIVE_ONLY и ICEBERG_ONLY используйте только для колонок, которые реально нужны одному движку.</t>
   </si>
   <si>
     <t>Шаг 12</t>
@@ -200,13 +200,13 @@
     <t>engine_scope</t>
   </si>
   <si>
-    <t>Опционально. both | hive_only | iceberg_only. Если пусто, трактуется как both.</t>
+    <t>Опционально. ALL | HIVE_ONLY | ICEBERG_ONLY. Если пусто, трактуется как ALL.</t>
   </si>
   <si>
     <t>derive</t>
   </si>
   <si>
-    <t>Формат: source_column="VALUE_DAY"; rule="YYYYMMDD". Используется только для derived-колонок.</t>
+    <t>Формат: source_column="VALUE_DAY"; rule="YYYYMMDD|YYYY|MM". Используется только для derived-колонок. source_column должен ссылаться на generated DATE/TIMESTAMP-колонку.</t>
   </si>
   <si>
     <t>Колонки листа queries</t>
@@ -248,7 +248,7 @@
     <t>derived from derived</t>
   </si>
   <si>
-    <t>Для v1 лучше не использовать. source_column должен ссылаться на обычную или FK-колонку этой же таблицы.</t>
+    <t>Запрещено. source_column должен ссылаться на generated DATE/TIMESTAMP-колонку этой же таблицы.</t>
   </si>
   <si>
     <t>partition columns</t>
@@ -309,13 +309,13 @@
   </si>
   <si>
     <t>source_column="VALUE_DAY";
-rule="YYYYMMDD"</t>
+rule="YYYYMMDD|YYYY|MM"</t>
   </si>
   <si>
     <t>OVERWRITE_TABLE</t>
   </si>
   <si>
-    <t>both</t>
+    <t>ALL</t>
   </si>
   <si>
     <t>YYYYMMDD</t>
@@ -338,10 +338,10 @@
     <t>OVERWRITE_PARTITIONS</t>
   </si>
   <si>
-    <t>hive_only</t>
-  </si>
-  <si>
-    <t>YEAR</t>
+    <t>HIVE_ONLY</t>
+  </si>
+  <si>
+    <t>YYYY</t>
   </si>
   <si>
     <t>FLOAT</t>
@@ -359,10 +359,10 @@
     <t>APPEND</t>
   </si>
   <si>
-    <t>iceberg_only</t>
-  </si>
-  <si>
-    <t>MONTH</t>
+    <t>ICEBERG_ONLY</t>
+  </si>
+  <si>
+    <t>MM</t>
   </si>
   <si>
     <t>DATE</t>
@@ -1753,7 +1753,7 @@
       </c>
       <c r="H2" s="8"/>
       <c r="I2" s="7" t="str">
-        <f>IF($F2&lt;&gt;"","Для foreign_key допустим только null_ratio=0..1. gen_data_type и output_data_type выводятся из parent column.",IF($H2&lt;&gt;"","Для derive укажите output_data_type и engine_scope; gen_data_type/constraints/foreign_key оставьте пустыми.",IFERROR(VLOOKUP($B2,'Constant List'!$A$2:$B$7,2,FALSE),"Тип генерации не заполнен")))</f>
+        <f>IF($F2&lt;&gt;"","Для foreign_key допустим только null_ratio=0..1. gen_data_type и output_data_type выводятся из parent column.",IF($H2&lt;&gt;"","Для derive укажите output_data_type и engine_scope; доступные rule: YYYYMMDD|YYYY|MM; gen_data_type/constraints/foreign_key оставьте пустыми.",IFERROR(VLOOKUP($B2,'Constant List'!$A$2:$B$7,2,FALSE),"Тип генерации не заполнен")))</f>
         <v>Формат constraints:
 null_ratio=0..1;
 is_unique=true/false;
@@ -1770,7 +1770,7 @@
       <c r="K2" s="9" t="str">
         <f>'Constant List'!$K$2</f>
         <v>source_column="VALUE_DAY";
-rule="YYYYMMDD"</v>
+rule="YYYYMMDD|YYYY|MM"</v>
       </c>
     </row>
     <row r="3" spans="1:11" ht="46.05" customHeight="1" x14ac:dyDescent="0.45">
@@ -1793,7 +1793,7 @@
       </c>
       <c r="H3" s="8"/>
       <c r="I3" s="7" t="str">
-        <f>IF($F3&lt;&gt;"","Для foreign_key допустим только null_ratio=0..1. gen_data_type и output_data_type выводятся из parent column.",IF($H3&lt;&gt;"","Для derive укажите output_data_type и engine_scope; gen_data_type/constraints/foreign_key оставьте пустыми.",IFERROR(VLOOKUP($B3,'Constant List'!$A$2:$B$7,2,FALSE),"Тип генерации не заполнен")))</f>
+        <f>IF($F3&lt;&gt;"","Для foreign_key допустим только null_ratio=0..1. gen_data_type и output_data_type выводятся из parent column.",IF($H3&lt;&gt;"","Для derive укажите output_data_type и engine_scope; доступные rule: YYYYMMDD|YYYY|MM; gen_data_type/constraints/foreign_key оставьте пустыми.",IFERROR(VLOOKUP($B3,'Constant List'!$A$2:$B$7,2,FALSE),"Тип генерации не заполнен")))</f>
         <v>Формат constraints:
 null_ratio=0..1;
 is_unique=true/false;
@@ -1810,7 +1810,7 @@
       <c r="K3" s="9" t="str">
         <f>'Constant List'!$K$2</f>
         <v>source_column="VALUE_DAY";
-rule="YYYYMMDD"</v>
+rule="YYYYMMDD|YYYY|MM"</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="28.05" customHeight="1" x14ac:dyDescent="0.45">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="H4" s="8"/>
       <c r="I4" s="7" t="str">
-        <f>IF($F4&lt;&gt;"","Для foreign_key допустим только null_ratio=0..1. gen_data_type и output_data_type выводятся из parent column.",IF($H4&lt;&gt;"","Для derive укажите output_data_type и engine_scope; gen_data_type/constraints/foreign_key оставьте пустыми.",IFERROR(VLOOKUP($B4,'Constant List'!$A$2:$B$7,2,FALSE),"Тип генерации не заполнен")))</f>
+        <f>IF($F4&lt;&gt;"","Для foreign_key допустим только null_ratio=0..1. gen_data_type и output_data_type выводятся из parent column.",IF($H4&lt;&gt;"","Для derive укажите output_data_type и engine_scope; доступные rule: YYYYMMDD|YYYY|MM; gen_data_type/constraints/foreign_key оставьте пустыми.",IFERROR(VLOOKUP($B4,'Constant List'!$A$2:$B$7,2,FALSE),"Тип генерации не заполнен")))</f>
         <v>Формат constraints:
 null_ratio=0..1;
 is_unique=true/false;
@@ -1850,7 +1850,7 @@
       <c r="K4" s="9" t="str">
         <f>'Constant List'!$K$2</f>
         <v>source_column="VALUE_DAY";
-rule="YYYYMMDD"</v>
+rule="YYYYMMDD|YYYY|MM"</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="46.05" customHeight="1" x14ac:dyDescent="0.45">
@@ -1873,7 +1873,7 @@
       </c>
       <c r="H5" s="8"/>
       <c r="I5" s="7" t="str">
-        <f>IF($F5&lt;&gt;"","Для foreign_key допустим только null_ratio=0..1. gen_data_type и output_data_type выводятся из parent column.",IF($H5&lt;&gt;"","Для derive укажите output_data_type и engine_scope; gen_data_type/constraints/foreign_key оставьте пустыми.",IFERROR(VLOOKUP($B5,'Constant List'!$A$2:$B$7,2,FALSE),"Тип генерации не заполнен")))</f>
+        <f>IF($F5&lt;&gt;"","Для foreign_key допустим только null_ratio=0..1. gen_data_type и output_data_type выводятся из parent column.",IF($H5&lt;&gt;"","Для derive укажите output_data_type и engine_scope; доступные rule: YYYYMMDD|YYYY|MM; gen_data_type/constraints/foreign_key оставьте пустыми.",IFERROR(VLOOKUP($B5,'Constant List'!$A$2:$B$7,2,FALSE),"Тип генерации не заполнен")))</f>
         <v>Формат constraints:
 null_ratio=0..1;
 is_unique=true/false;
@@ -1891,7 +1891,7 @@
       <c r="K5" s="9" t="str">
         <f>'Constant List'!$K$2</f>
         <v>source_column="VALUE_DAY";
-rule="YYYYMMDD"</v>
+rule="YYYYMMDD|YYYY|MM"</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="28.05" customHeight="1" x14ac:dyDescent="0.45">
@@ -1912,8 +1912,8 @@
         <v>122</v>
       </c>
       <c r="I6" s="7" t="str">
-        <f>IF($F6&lt;&gt;"","Для foreign_key допустим только null_ratio=0..1. gen_data_type и output_data_type выводятся из parent column.",IF($H6&lt;&gt;"","Для derive укажите output_data_type и engine_scope; gen_data_type/constraints/foreign_key оставьте пустыми.",IFERROR(VLOOKUP($B6,'Constant List'!$A$2:$B$7,2,FALSE),"Тип генерации не заполнен")))</f>
-        <v>Для derive укажите output_data_type и engine_scope; gen_data_type/constraints/foreign_key оставьте пустыми.</v>
+        <f>IF($F6&lt;&gt;"","Для foreign_key допустим только null_ratio=0..1. gen_data_type и output_data_type выводятся из parent column.",IF($H6&lt;&gt;"","Для derive укажите output_data_type и engine_scope; доступные rule: YYYYMMDD|YYYY|MM; gen_data_type/constraints/foreign_key оставьте пустыми.",IFERROR(VLOOKUP($B6,'Constant List'!$A$2:$B$7,2,FALSE),"Тип генерации не заполнен")))</f>
+        <v>Для derive укажите output_data_type и engine_scope; доступные rule: YYYYMMDD|YYYY|MM; gen_data_type/constraints/foreign_key оставьте пустыми.</v>
       </c>
       <c r="J6" s="7" t="str">
         <f>'Constant List'!$J$2</f>
@@ -1924,7 +1924,7 @@
       <c r="K6" s="9" t="str">
         <f>'Constant List'!$K$2</f>
         <v>source_column="VALUE_DAY";
-rule="YYYYMMDD"</v>
+rule="YYYYMMDD|YYYY|MM"</v>
       </c>
     </row>
   </sheetData>
@@ -1934,7 +1934,7 @@
       <formula1>"STRING,INT,FLOAT,DATE,TIMESTAMP,BOOLEAN"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" sqref="G2:G500" xr:uid="{00000000-0002-0000-0400-000001000000}">
-      <formula1>"both,hive_only,iceberg_only"</formula1>
+      <formula1>"ALL,HIVE_ONLY,ICEBERG_ONLY"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" sqref="D2:D500" xr:uid="{00000000-0002-0000-0400-000002000000}">
       <formula1>"TRUE,FALSE"</formula1>
@@ -2016,7 +2016,7 @@
       </c>
       <c r="H2" s="8"/>
       <c r="I2" s="7" t="str">
-        <f>IF($F2&lt;&gt;"","Для foreign_key допустим только null_ratio=0..1. gen_data_type и output_data_type выводятся из parent column.",IF($H2&lt;&gt;"","Для derive укажите output_data_type и engine_scope; gen_data_type/constraints/foreign_key оставьте пустыми.",IFERROR(VLOOKUP($B2,'Constant List'!$A$2:$B$7,2,FALSE),"Тип генерации не заполнен")))</f>
+        <f>IF($F2&lt;&gt;"","Для foreign_key допустим только null_ratio=0..1. gen_data_type и output_data_type выводятся из parent column.",IF($H2&lt;&gt;"","Для derive укажите output_data_type и engine_scope; доступные rule: YYYYMMDD|YYYY|MM; gen_data_type/constraints/foreign_key оставьте пустыми.",IFERROR(VLOOKUP($B2,'Constant List'!$A$2:$B$7,2,FALSE),"Тип генерации не заполнен")))</f>
         <v>Формат constraints:
 null_ratio=0..1;
 is_unique=true/false;
@@ -2035,7 +2035,7 @@
       <c r="K2" s="9" t="str">
         <f>'Constant List'!$K$2</f>
         <v>source_column="VALUE_DAY";
-rule="YYYYMMDD"</v>
+rule="YYYYMMDD|YYYY|MM"</v>
       </c>
     </row>
     <row r="3" spans="1:11" ht="46.05" customHeight="1" x14ac:dyDescent="0.45">
@@ -2054,7 +2054,7 @@
       </c>
       <c r="H3" s="8"/>
       <c r="I3" s="7" t="str">
-        <f>IF($F3&lt;&gt;"","Для foreign_key допустим только null_ratio=0..1. gen_data_type и output_data_type выводятся из parent column.",IF($H3&lt;&gt;"","Для derive укажите output_data_type и engine_scope; gen_data_type/constraints/foreign_key оставьте пустыми.",IFERROR(VLOOKUP($B3,'Constant List'!$A$2:$B$7,2,FALSE),"Тип генерации не заполнен")))</f>
+        <f>IF($F3&lt;&gt;"","Для foreign_key допустим только null_ratio=0..1. gen_data_type и output_data_type выводятся из parent column.",IF($H3&lt;&gt;"","Для derive укажите output_data_type и engine_scope; доступные rule: YYYYMMDD|YYYY|MM; gen_data_type/constraints/foreign_key оставьте пустыми.",IFERROR(VLOOKUP($B3,'Constant List'!$A$2:$B$7,2,FALSE),"Тип генерации не заполнен")))</f>
         <v>Для foreign_key допустим только null_ratio=0..1. gen_data_type и output_data_type выводятся из parent column.</v>
       </c>
       <c r="J3" s="7" t="str">
@@ -2066,7 +2066,7 @@
       <c r="K3" s="9" t="str">
         <f>'Constant List'!$K$2</f>
         <v>source_column="VALUE_DAY";
-rule="YYYYMMDD"</v>
+rule="YYYYMMDD|YYYY|MM"</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="46.05" customHeight="1" x14ac:dyDescent="0.45">
@@ -2089,7 +2089,7 @@
       </c>
       <c r="H4" s="8"/>
       <c r="I4" s="7" t="str">
-        <f>IF($F4&lt;&gt;"","Для foreign_key допустим только null_ratio=0..1. gen_data_type и output_data_type выводятся из parent column.",IF($H4&lt;&gt;"","Для derive укажите output_data_type и engine_scope; gen_data_type/constraints/foreign_key оставьте пустыми.",IFERROR(VLOOKUP($B4,'Constant List'!$A$2:$B$7,2,FALSE),"Тип генерации не заполнен")))</f>
+        <f>IF($F4&lt;&gt;"","Для foreign_key допустим только null_ratio=0..1. gen_data_type и output_data_type выводятся из parent column.",IF($H4&lt;&gt;"","Для derive укажите output_data_type и engine_scope; доступные rule: YYYYMMDD|YYYY|MM; gen_data_type/constraints/foreign_key оставьте пустыми.",IFERROR(VLOOKUP($B4,'Constant List'!$A$2:$B$7,2,FALSE),"Тип генерации не заполнен")))</f>
         <v>Формат constraints:
 null_ratio=0..1;
 is_unique=true/false;
@@ -2106,7 +2106,7 @@
       <c r="K4" s="9" t="str">
         <f>'Constant List'!$K$2</f>
         <v>source_column="VALUE_DAY";
-rule="YYYYMMDD"</v>
+rule="YYYYMMDD|YYYY|MM"</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="46.05" customHeight="1" x14ac:dyDescent="0.45">
@@ -2129,7 +2129,7 @@
       </c>
       <c r="H5" s="8"/>
       <c r="I5" s="7" t="str">
-        <f>IF($F5&lt;&gt;"","Для foreign_key допустим только null_ratio=0..1. gen_data_type и output_data_type выводятся из parent column.",IF($H5&lt;&gt;"","Для derive укажите output_data_type и engine_scope; gen_data_type/constraints/foreign_key оставьте пустыми.",IFERROR(VLOOKUP($B5,'Constant List'!$A$2:$B$7,2,FALSE),"Тип генерации не заполнен")))</f>
+        <f>IF($F5&lt;&gt;"","Для foreign_key допустим только null_ratio=0..1. gen_data_type и output_data_type выводятся из parent column.",IF($H5&lt;&gt;"","Для derive укажите output_data_type и engine_scope; доступные rule: YYYYMMDD|YYYY|MM; gen_data_type/constraints/foreign_key оставьте пустыми.",IFERROR(VLOOKUP($B5,'Constant List'!$A$2:$B$7,2,FALSE),"Тип генерации не заполнен")))</f>
         <v>Формат constraints:
 null_ratio=0..1;
 is_unique=true/false;
@@ -2148,7 +2148,7 @@
       <c r="K5" s="9" t="str">
         <f>'Constant List'!$K$2</f>
         <v>source_column="VALUE_DAY";
-rule="YYYYMMDD"</v>
+rule="YYYYMMDD|YYYY|MM"</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="28.05" customHeight="1" x14ac:dyDescent="0.45">
@@ -2171,7 +2171,7 @@
       </c>
       <c r="H6" s="8"/>
       <c r="I6" s="7" t="str">
-        <f>IF($F6&lt;&gt;"","Для foreign_key допустим только null_ratio=0..1. gen_data_type и output_data_type выводятся из parent column.",IF($H6&lt;&gt;"","Для derive укажите output_data_type и engine_scope; gen_data_type/constraints/foreign_key оставьте пустыми.",IFERROR(VLOOKUP($B6,'Constant List'!$A$2:$B$7,2,FALSE),"Тип генерации не заполнен")))</f>
+        <f>IF($F6&lt;&gt;"","Для foreign_key допустим только null_ratio=0..1. gen_data_type и output_data_type выводятся из parent column.",IF($H6&lt;&gt;"","Для derive укажите output_data_type и engine_scope; доступные rule: YYYYMMDD|YYYY|MM; gen_data_type/constraints/foreign_key оставьте пустыми.",IFERROR(VLOOKUP($B6,'Constant List'!$A$2:$B$7,2,FALSE),"Тип генерации не заполнен")))</f>
         <v>Формат constraints:
 null_ratio=0..1;
 is_unique=true/false;
@@ -2190,7 +2190,7 @@
       <c r="K6" s="9" t="str">
         <f>'Constant List'!$K$2</f>
         <v>source_column="VALUE_DAY";
-rule="YYYYMMDD"</v>
+rule="YYYYMMDD|YYYY|MM"</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="46.05" customHeight="1" x14ac:dyDescent="0.45">
@@ -2213,7 +2213,7 @@
       </c>
       <c r="H7" s="8"/>
       <c r="I7" s="7" t="str">
-        <f>IF($F7&lt;&gt;"","Для foreign_key допустим только null_ratio=0..1. gen_data_type и output_data_type выводятся из parent column.",IF($H7&lt;&gt;"","Для derive укажите output_data_type и engine_scope; gen_data_type/constraints/foreign_key оставьте пустыми.",IFERROR(VLOOKUP($B7,'Constant List'!$A$2:$B$7,2,FALSE),"Тип генерации не заполнен")))</f>
+        <f>IF($F7&lt;&gt;"","Для foreign_key допустим только null_ratio=0..1. gen_data_type и output_data_type выводятся из parent column.",IF($H7&lt;&gt;"","Для derive укажите output_data_type и engine_scope; доступные rule: YYYYMMDD|YYYY|MM; gen_data_type/constraints/foreign_key оставьте пустыми.",IFERROR(VLOOKUP($B7,'Constant List'!$A$2:$B$7,2,FALSE),"Тип генерации не заполнен")))</f>
         <v>Формат constraints:
 null_ratio=0..1;
 is_unique=true/false;
@@ -2232,7 +2232,7 @@
       <c r="K7" s="9" t="str">
         <f>'Constant List'!$K$2</f>
         <v>source_column="VALUE_DAY";
-rule="YYYYMMDD"</v>
+rule="YYYYMMDD|YYYY|MM"</v>
       </c>
     </row>
     <row r="8" spans="1:11" ht="28.05" customHeight="1" x14ac:dyDescent="0.45">
@@ -2255,7 +2255,7 @@
       </c>
       <c r="H8" s="8"/>
       <c r="I8" s="7" t="str">
-        <f>IF($F8&lt;&gt;"","Для foreign_key допустим только null_ratio=0..1. gen_data_type и output_data_type выводятся из parent column.",IF($H8&lt;&gt;"","Для derive укажите output_data_type и engine_scope; gen_data_type/constraints/foreign_key оставьте пустыми.",IFERROR(VLOOKUP($B8,'Constant List'!$A$2:$B$7,2,FALSE),"Тип генерации не заполнен")))</f>
+        <f>IF($F8&lt;&gt;"","Для foreign_key допустим только null_ratio=0..1. gen_data_type и output_data_type выводятся из parent column.",IF($H8&lt;&gt;"","Для derive укажите output_data_type и engine_scope; доступные rule: YYYYMMDD|YYYY|MM; gen_data_type/constraints/foreign_key оставьте пустыми.",IFERROR(VLOOKUP($B8,'Constant List'!$A$2:$B$7,2,FALSE),"Тип генерации не заполнен")))</f>
         <v>Формат constraints:
 null_ratio=0..1;
 is_unique=true/false;
@@ -2272,7 +2272,7 @@
       <c r="K8" s="9" t="str">
         <f>'Constant List'!$K$2</f>
         <v>source_column="VALUE_DAY";
-rule="YYYYMMDD"</v>
+rule="YYYYMMDD|YYYY|MM"</v>
       </c>
     </row>
   </sheetData>
@@ -2282,7 +2282,7 @@
       <formula1>"STRING,INT,FLOAT,DATE,TIMESTAMP,BOOLEAN"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" sqref="G2:G500" xr:uid="{00000000-0002-0000-0500-000001000000}">
-      <formula1>"both,hive_only,iceberg_only"</formula1>
+      <formula1>"ALL,HIVE_ONLY,ICEBERG_ONLY"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" sqref="D2:D500" xr:uid="{00000000-0002-0000-0500-000002000000}">
       <formula1>"TRUE,FALSE"</formula1>

--- a/datagen/params/data_gen.xlsx
+++ b/datagen/params/data_gen.xlsx
@@ -820,7 +820,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>В sheet таблицы каждая строка должна быть ровно одного типа: generated, foreign key или derived.</t>
+          <t>В sheet таблицы каждая строка должна быть ровно одного типа: generated, reference или derived.</t>
         </is>
       </c>
     </row>
@@ -832,7 +832,7 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>generated: заполнены column_name + gen_data_type. output_data_type опционален, остальные специальные поля пустые.</t>
+          <t>generated: заполнены column_name + gen_data_type. output_data_type опционален, reference и derive пустые.</t>
         </is>
       </c>
     </row>
@@ -844,7 +844,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>foreign key: заполнен только foreign_key. gen_data_type и output_data_type не указываются вручную, constraints допускает только null_ratio.</t>
+          <t>reference: заполнен только reference. gen_data_type и output_data_type не указываются вручную, constraints допускает только null_ratio.</t>
         </is>
       </c>
     </row>
@@ -856,7 +856,7 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>derived: заполнены derive + output_data_type. gen_data_type, constraints и foreign_key остаются пустыми.</t>
+          <t>derived: заполнены derive + output_data_type. gen_data_type, constraints и reference остаются пустыми.</t>
         </is>
       </c>
     </row>
@@ -1010,19 +1010,19 @@
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>Опционально для generated, обязательно для derived, пусто для foreign key.</t>
+          <t>Опционально для generated, обязательно для derived, пусто для reference.</t>
         </is>
       </c>
     </row>
     <row r="29" s="6">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>is_primary_key</t>
+          <t>removed</t>
         </is>
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>Опционально. TRUE только для generated-колонок. Для PK система сама применяет null_ratio=0 и is_unique=true.</t>
+          <t>Не используется. Уникальность задаётся constraints.is_unique=true.</t>
         </is>
       </c>
     </row>
@@ -1034,19 +1034,19 @@
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>Опционально только для generated. Формат key=value; key=value. Для foreign key допустим только null_ratio, для derived поле должно быть пустым.</t>
+          <t>Опционально только для generated. Формат key=value; key=value. Для reference допустим только null_ratio, для derived поле должно быть пустым.</t>
         </is>
       </c>
     </row>
     <row r="31" s="6">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>foreign_key</t>
+          <t>reference</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>Формат: table_name="..."; column_name="..."; relation_type="ONE_TO_MANY|ONE_TO_ONE".</t>
+          <t>Формат: table_name="..."; column_name="..."; cardinality="ONE_TO_MANY|ONE_TO_ONE".</t>
         </is>
       </c>
     </row>
@@ -1215,38 +1215,30 @@
     <row r="48" ht="36" customHeight="1" s="6">
       <c r="A48" s="16" t="inlineStr">
         <is>
-          <t>engine_scope=ICEBERG_ONLY</t>
+          <t>cardinality=ONE_TO_MANY</t>
         </is>
       </c>
       <c r="B48" s="21" t="inlineStr">
         <is>
-          <t>Колонка загружается только в Iceberg. Не возвращайте её в compare SQL или добавьте alias в iceberg_exclude_columns.</t>
+          <t>Reference-колонка может повторять non-null значения родительской колонки.</t>
         </is>
       </c>
     </row>
     <row r="49" ht="36" customHeight="1" s="6">
       <c r="A49" s="16" t="inlineStr">
         <is>
-          <t>relation_type=ONE_TO_MANY</t>
+          <t>cardinality=ONE_TO_ONE</t>
         </is>
       </c>
       <c r="B49" s="21" t="inlineStr">
         <is>
-          <t>FK-колонка может повторять значения родительской колонки.</t>
+          <t>Reference-колонка использует distinct non-null родительские значения без повторов.</t>
         </is>
       </c>
     </row>
     <row r="50" ht="36" customHeight="1" s="6">
-      <c r="A50" s="16" t="inlineStr">
-        <is>
-          <t>relation_type=ONE_TO_ONE</t>
-        </is>
-      </c>
-      <c r="B50" s="21" t="inlineStr">
-        <is>
-          <t>FK-колонка использует родительские значения без повторов; у родителя должно хватить уникальных значений.</t>
-        </is>
-      </c>
+      <c r="A50" s="16" t="n"/>
+      <c r="B50" s="21" t="n"/>
     </row>
     <row r="51" ht="36" customHeight="1" s="6">
       <c r="A51" s="16" t="inlineStr">
@@ -1371,22 +1363,18 @@
     <row r="61" ht="36" customHeight="1" s="6">
       <c r="A61" s="18" t="inlineStr">
         <is>
-          <t>Corner cases</t>
-        </is>
-      </c>
-      <c r="B61" s="18" t="n"/>
+          <t>reference + derive</t>
+        </is>
+      </c>
+      <c r="B61" s="18" t="inlineStr">
+        <is>
+          <t>Одновременно запрещены.</t>
+        </is>
+      </c>
     </row>
     <row r="62" ht="36" customHeight="1" s="6">
-      <c r="A62" s="16" t="inlineStr">
-        <is>
-          <t>foreign_key + derive</t>
-        </is>
-      </c>
-      <c r="B62" s="21" t="inlineStr">
-        <is>
-          <t>Одновременно запрещены.</t>
-        </is>
-      </c>
+      <c r="A62" s="16" t="n"/>
+      <c r="B62" s="21" t="n"/>
     </row>
     <row r="63" ht="36" customHeight="1" s="6">
       <c r="A63" s="16" t="inlineStr">
@@ -1494,7 +1482,7 @@
       </c>
       <c r="J1" s="13" t="inlineStr">
         <is>
-          <t>Foreign Key Example</t>
+          <t>Reference Example</t>
         </is>
       </c>
       <c r="K1" s="13" t="inlineStr">
@@ -1555,7 +1543,7 @@
         <is>
           <t>table_name="company_groups";
 column_name="INN";
-relation_type="ONE_TO_MANY|ONE_TO_ONE"</t>
+cardinality="ONE_TO_MANY|ONE_TO_ONE"</t>
         </is>
       </c>
       <c r="K2" s="13" t="inlineStr">
@@ -1734,7 +1722,7 @@
       </c>
       <c r="Q6" s="21" t="inlineStr">
         <is>
-          <t>Итоговый тип. Обязателен для derived, пустой для foreign_key.</t>
+          <t>Итоговый тип. Обязателен для derived, пустой для reference.</t>
         </is>
       </c>
     </row>
@@ -1766,12 +1754,12 @@
     <row r="8" ht="44" customHeight="1" s="6">
       <c r="P8" s="16" t="inlineStr">
         <is>
-          <t>foreign_key</t>
+          <t>reference</t>
         </is>
       </c>
       <c r="Q8" s="21" t="inlineStr">
         <is>
-          <t>table_name="..."; column_name="..."; relation_type="ONE_TO_MANY|ONE_TO_ONE".</t>
+          <t>table_name="..."; column_name="..."; cardinality="ONE_TO_MANY|ONE_TO_ONE".</t>
         </is>
       </c>
     </row>
@@ -2039,11 +2027,7 @@
           <t>output_data_type</t>
         </is>
       </c>
-      <c r="D1" s="10" t="inlineStr">
-        <is>
-          <t>is_primary_key</t>
-        </is>
-      </c>
+      <c r="D1" s="10" t="n"/>
       <c r="E1" s="10" t="inlineStr">
         <is>
           <t>constraints</t>
@@ -2051,7 +2035,7 @@
       </c>
       <c r="F1" s="10" t="inlineStr">
         <is>
-          <t>foreign_key</t>
+          <t>reference</t>
         </is>
       </c>
       <c r="G1" s="10" t="inlineStr">
@@ -2071,7 +2055,7 @@
       </c>
       <c r="J1" s="11" t="inlineStr">
         <is>
-          <t>Пример заполнения foreign_key</t>
+          <t>Пример заполнения reference</t>
         </is>
       </c>
       <c r="K1" s="12" t="inlineStr">
@@ -2092,12 +2076,10 @@
         </is>
       </c>
       <c r="C2" s="8" t="n"/>
-      <c r="D2" s="8" t="b">
-        <v>1</v>
-      </c>
+      <c r="D2" s="8" t="n"/>
       <c r="E2" s="8" t="inlineStr">
         <is>
-          <t>digits_count=10</t>
+          <t>digits_count=10; is_unique=true</t>
         </is>
       </c>
       <c r="F2" s="8" t="n"/>
@@ -2108,7 +2090,7 @@
       </c>
       <c r="H2" s="8" t="n"/>
       <c r="I2" s="7">
-        <f>IF($F2&lt;&gt;"","Для foreign_key допустим только null_ratio=0..1. gen_data_type и output_data_type выводятся из parent column.",IF($H2&lt;&gt;"","Для derive укажите output_data_type и engine_scope; доступные rule: YYYYMMDD|YYYY|MM; gen_data_type/constraints/foreign_key оставьте пустыми.",IFERROR(VLOOKUP($B2,'Constant List'!$A$2:$B$7,2,FALSE),"Тип генерации не заполнен")))</f>
+        <f>IF($F2&lt;&gt;"","Для reference допустим только null_ratio=0..1. gen_data_type и output_data_type выводятся из parent column.",IF($H2&lt;&gt;"","Для derive укажите output_data_type и engine_scope; доступные rule: YYYYMMDD|YYYY|MM; gen_data_type/constraints/reference оставьте пустыми.",IFERROR(VLOOKUP($B2,'Constant List'!$A$2:$B$7,2,FALSE),"Тип генерации не заполнен")))</f>
         <v/>
       </c>
       <c r="J2" s="7">
@@ -2146,7 +2128,7 @@
       </c>
       <c r="H3" s="8" t="n"/>
       <c r="I3" s="7">
-        <f>IF($F3&lt;&gt;"","Для foreign_key допустим только null_ratio=0..1. gen_data_type и output_data_type выводятся из parent column.",IF($H3&lt;&gt;"","Для derive укажите output_data_type и engine_scope; доступные rule: YYYYMMDD|YYYY|MM; gen_data_type/constraints/foreign_key оставьте пустыми.",IFERROR(VLOOKUP($B3,'Constant List'!$A$2:$B$7,2,FALSE),"Тип генерации не заполнен")))</f>
+        <f>IF($F3&lt;&gt;"","Для reference допустим только null_ratio=0..1. gen_data_type и output_data_type выводятся из parent column.",IF($H3&lt;&gt;"","Для derive укажите output_data_type и engine_scope; доступные rule: YYYYMMDD|YYYY|MM; gen_data_type/constraints/reference оставьте пустыми.",IFERROR(VLOOKUP($B3,'Constant List'!$A$2:$B$7,2,FALSE),"Тип генерации не заполнен")))</f>
         <v/>
       </c>
       <c r="J3" s="7">
@@ -2184,7 +2166,7 @@
       </c>
       <c r="H4" s="8" t="n"/>
       <c r="I4" s="7">
-        <f>IF($F4&lt;&gt;"","Для foreign_key допустим только null_ratio=0..1. gen_data_type и output_data_type выводятся из parent column.",IF($H4&lt;&gt;"","Для derive укажите output_data_type и engine_scope; доступные rule: YYYYMMDD|YYYY|MM; gen_data_type/constraints/foreign_key оставьте пустыми.",IFERROR(VLOOKUP($B4,'Constant List'!$A$2:$B$7,2,FALSE),"Тип генерации не заполнен")))</f>
+        <f>IF($F4&lt;&gt;"","Для reference допустим только null_ratio=0..1. gen_data_type и output_data_type выводятся из parent column.",IF($H4&lt;&gt;"","Для derive укажите output_data_type и engine_scope; доступные rule: YYYYMMDD|YYYY|MM; gen_data_type/constraints/reference оставьте пустыми.",IFERROR(VLOOKUP($B4,'Constant List'!$A$2:$B$7,2,FALSE),"Тип генерации не заполнен")))</f>
         <v/>
       </c>
       <c r="J4" s="7">
@@ -2222,7 +2204,7 @@
       </c>
       <c r="H5" s="8" t="n"/>
       <c r="I5" s="7">
-        <f>IF($F5&lt;&gt;"","Для foreign_key допустим только null_ratio=0..1. gen_data_type и output_data_type выводятся из parent column.",IF($H5&lt;&gt;"","Для derive укажите output_data_type и engine_scope; доступные rule: YYYYMMDD|YYYY|MM; gen_data_type/constraints/foreign_key оставьте пустыми.",IFERROR(VLOOKUP($B5,'Constant List'!$A$2:$B$7,2,FALSE),"Тип генерации не заполнен")))</f>
+        <f>IF($F5&lt;&gt;"","Для reference допустим только null_ratio=0..1. gen_data_type и output_data_type выводятся из parent column.",IF($H5&lt;&gt;"","Для derive укажите output_data_type и engine_scope; доступные rule: YYYYMMDD|YYYY|MM; gen_data_type/constraints/reference оставьте пустыми.",IFERROR(VLOOKUP($B5,'Constant List'!$A$2:$B$7,2,FALSE),"Тип генерации не заполнен")))</f>
         <v/>
       </c>
       <c r="J5" s="7">
@@ -2260,7 +2242,7 @@
         </is>
       </c>
       <c r="I6" s="7">
-        <f>IF($F6&lt;&gt;"","Для foreign_key допустим только null_ratio=0..1. gen_data_type и output_data_type выводятся из parent column.",IF($H6&lt;&gt;"","Для derive укажите output_data_type и engine_scope; доступные rule: YYYYMMDD|YYYY|MM; gen_data_type/constraints/foreign_key оставьте пустыми.",IFERROR(VLOOKUP($B6,'Constant List'!$A$2:$B$7,2,FALSE),"Тип генерации не заполнен")))</f>
+        <f>IF($F6&lt;&gt;"","Для reference допустим только null_ratio=0..1. gen_data_type и output_data_type выводятся из parent column.",IF($H6&lt;&gt;"","Для derive укажите output_data_type и engine_scope; доступные rule: YYYYMMDD|YYYY|MM; gen_data_type/constraints/reference оставьте пустыми.",IFERROR(VLOOKUP($B6,'Constant List'!$A$2:$B$7,2,FALSE),"Тип генерации не заполнен")))</f>
         <v/>
       </c>
       <c r="J6" s="7">
@@ -2326,11 +2308,7 @@
           <t>output_data_type</t>
         </is>
       </c>
-      <c r="D1" s="10" t="inlineStr">
-        <is>
-          <t>is_primary_key</t>
-        </is>
-      </c>
+      <c r="D1" s="10" t="n"/>
       <c r="E1" s="10" t="inlineStr">
         <is>
           <t>constraints</t>
@@ -2338,7 +2316,7 @@
       </c>
       <c r="F1" s="10" t="inlineStr">
         <is>
-          <t>foreign_key</t>
+          <t>reference</t>
         </is>
       </c>
       <c r="G1" s="10" t="inlineStr">
@@ -2358,7 +2336,7 @@
       </c>
       <c r="J1" s="11" t="inlineStr">
         <is>
-          <t>Пример заполнения foreign_key</t>
+          <t>Пример заполнения reference</t>
         </is>
       </c>
       <c r="K1" s="12" t="inlineStr">
@@ -2393,7 +2371,7 @@
       </c>
       <c r="H2" s="8" t="n"/>
       <c r="I2" s="7">
-        <f>IF($F2&lt;&gt;"","Для foreign_key допустим только null_ratio=0..1. gen_data_type и output_data_type выводятся из parent column.",IF($H2&lt;&gt;"","Для derive укажите output_data_type и engine_scope; доступные rule: YYYYMMDD|YYYY|MM; gen_data_type/constraints/foreign_key оставьте пустыми.",IFERROR(VLOOKUP($B2,'Constant List'!$A$2:$B$7,2,FALSE),"Тип генерации не заполнен")))</f>
+        <f>IF($F2&lt;&gt;"","Для reference допустим только null_ratio=0..1. gen_data_type и output_data_type выводятся из parent column.",IF($H2&lt;&gt;"","Для derive укажите output_data_type и engine_scope; доступные rule: YYYYMMDD|YYYY|MM; gen_data_type/constraints/reference оставьте пустыми.",IFERROR(VLOOKUP($B2,'Constant List'!$A$2:$B$7,2,FALSE),"Тип генерации не заполнен")))</f>
         <v/>
       </c>
       <c r="J2" s="7">
@@ -2417,7 +2395,7 @@
       <c r="E3" s="8" t="n"/>
       <c r="F3" s="8" t="inlineStr">
         <is>
-          <t>table_name="company_groups"; column_name="INN"; relation_type="ONE_TO_MANY"</t>
+          <t>table_name="company_groups"; column_name="INN"; cardinality="ONE_TO_MANY"</t>
         </is>
       </c>
       <c r="G3" s="8" t="inlineStr">
@@ -2427,7 +2405,7 @@
       </c>
       <c r="H3" s="8" t="n"/>
       <c r="I3" s="7">
-        <f>IF($F3&lt;&gt;"","Для foreign_key допустим только null_ratio=0..1. gen_data_type и output_data_type выводятся из parent column.",IF($H3&lt;&gt;"","Для derive укажите output_data_type и engine_scope; доступные rule: YYYYMMDD|YYYY|MM; gen_data_type/constraints/foreign_key оставьте пустыми.",IFERROR(VLOOKUP($B3,'Constant List'!$A$2:$B$7,2,FALSE),"Тип генерации не заполнен")))</f>
+        <f>IF($F3&lt;&gt;"","Для reference допустим только null_ratio=0..1. gen_data_type и output_data_type выводятся из parent column.",IF($H3&lt;&gt;"","Для derive укажите output_data_type и engine_scope; доступные rule: YYYYMMDD|YYYY|MM; gen_data_type/constraints/reference оставьте пустыми.",IFERROR(VLOOKUP($B3,'Constant List'!$A$2:$B$7,2,FALSE),"Тип генерации не заполнен")))</f>
         <v/>
       </c>
       <c r="J3" s="7">
@@ -2465,7 +2443,7 @@
       </c>
       <c r="H4" s="8" t="n"/>
       <c r="I4" s="7">
-        <f>IF($F4&lt;&gt;"","Для foreign_key допустим только null_ratio=0..1. gen_data_type и output_data_type выводятся из parent column.",IF($H4&lt;&gt;"","Для derive укажите output_data_type и engine_scope; доступные rule: YYYYMMDD|YYYY|MM; gen_data_type/constraints/foreign_key оставьте пустыми.",IFERROR(VLOOKUP($B4,'Constant List'!$A$2:$B$7,2,FALSE),"Тип генерации не заполнен")))</f>
+        <f>IF($F4&lt;&gt;"","Для reference допустим только null_ratio=0..1. gen_data_type и output_data_type выводятся из parent column.",IF($H4&lt;&gt;"","Для derive укажите output_data_type и engine_scope; доступные rule: YYYYMMDD|YYYY|MM; gen_data_type/constraints/reference оставьте пустыми.",IFERROR(VLOOKUP($B4,'Constant List'!$A$2:$B$7,2,FALSE),"Тип генерации не заполнен")))</f>
         <v/>
       </c>
       <c r="J4" s="7">
@@ -2503,7 +2481,7 @@
       </c>
       <c r="H5" s="8" t="n"/>
       <c r="I5" s="7">
-        <f>IF($F5&lt;&gt;"","Для foreign_key допустим только null_ratio=0..1. gen_data_type и output_data_type выводятся из parent column.",IF($H5&lt;&gt;"","Для derive укажите output_data_type и engine_scope; доступные rule: YYYYMMDD|YYYY|MM; gen_data_type/constraints/foreign_key оставьте пустыми.",IFERROR(VLOOKUP($B5,'Constant List'!$A$2:$B$7,2,FALSE),"Тип генерации не заполнен")))</f>
+        <f>IF($F5&lt;&gt;"","Для reference допустим только null_ratio=0..1. gen_data_type и output_data_type выводятся из parent column.",IF($H5&lt;&gt;"","Для derive укажите output_data_type и engine_scope; доступные rule: YYYYMMDD|YYYY|MM; gen_data_type/constraints/reference оставьте пустыми.",IFERROR(VLOOKUP($B5,'Constant List'!$A$2:$B$7,2,FALSE),"Тип генерации не заполнен")))</f>
         <v/>
       </c>
       <c r="J5" s="7">
@@ -2541,7 +2519,7 @@
       </c>
       <c r="H6" s="8" t="n"/>
       <c r="I6" s="7">
-        <f>IF($F6&lt;&gt;"","Для foreign_key допустим только null_ratio=0..1. gen_data_type и output_data_type выводятся из parent column.",IF($H6&lt;&gt;"","Для derive укажите output_data_type и engine_scope; доступные rule: YYYYMMDD|YYYY|MM; gen_data_type/constraints/foreign_key оставьте пустыми.",IFERROR(VLOOKUP($B6,'Constant List'!$A$2:$B$7,2,FALSE),"Тип генерации не заполнен")))</f>
+        <f>IF($F6&lt;&gt;"","Для reference допустим только null_ratio=0..1. gen_data_type и output_data_type выводятся из parent column.",IF($H6&lt;&gt;"","Для derive укажите output_data_type и engine_scope; доступные rule: YYYYMMDD|YYYY|MM; gen_data_type/constraints/reference оставьте пустыми.",IFERROR(VLOOKUP($B6,'Constant List'!$A$2:$B$7,2,FALSE),"Тип генерации не заполнен")))</f>
         <v/>
       </c>
       <c r="J6" s="7">
@@ -2579,7 +2557,7 @@
       </c>
       <c r="H7" s="8" t="n"/>
       <c r="I7" s="7">
-        <f>IF($F7&lt;&gt;"","Для foreign_key допустим только null_ratio=0..1. gen_data_type и output_data_type выводятся из parent column.",IF($H7&lt;&gt;"","Для derive укажите output_data_type и engine_scope; доступные rule: YYYYMMDD|YYYY|MM; gen_data_type/constraints/foreign_key оставьте пустыми.",IFERROR(VLOOKUP($B7,'Constant List'!$A$2:$B$7,2,FALSE),"Тип генерации не заполнен")))</f>
+        <f>IF($F7&lt;&gt;"","Для reference допустим только null_ratio=0..1. gen_data_type и output_data_type выводятся из parent column.",IF($H7&lt;&gt;"","Для derive укажите output_data_type и engine_scope; доступные rule: YYYYMMDD|YYYY|MM; gen_data_type/constraints/reference оставьте пустыми.",IFERROR(VLOOKUP($B7,'Constant List'!$A$2:$B$7,2,FALSE),"Тип генерации не заполнен")))</f>
         <v/>
       </c>
       <c r="J7" s="7">
@@ -2617,7 +2595,7 @@
       </c>
       <c r="H8" s="8" t="n"/>
       <c r="I8" s="7">
-        <f>IF($F8&lt;&gt;"","Для foreign_key допустим только null_ratio=0..1. gen_data_type и output_data_type выводятся из parent column.",IF($H8&lt;&gt;"","Для derive укажите output_data_type и engine_scope; доступные rule: YYYYMMDD|YYYY|MM; gen_data_type/constraints/foreign_key оставьте пустыми.",IFERROR(VLOOKUP($B8,'Constant List'!$A$2:$B$7,2,FALSE),"Тип генерации не заполнен")))</f>
+        <f>IF($F8&lt;&gt;"","Для reference допустим только null_ratio=0..1. gen_data_type и output_data_type выводятся из parent column.",IF($H8&lt;&gt;"","Для derive укажите output_data_type и engine_scope; доступные rule: YYYYMMDD|YYYY|MM; gen_data_type/constraints/reference оставьте пустыми.",IFERROR(VLOOKUP($B8,'Constant List'!$A$2:$B$7,2,FALSE),"Тип генерации не заполнен")))</f>
         <v/>
       </c>
       <c r="J8" s="7">
